--- a/04_Figures/F06_prediction/modules/T2/lasso/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/T2/lasso/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -152,6 +152,12 @@
     <t xml:space="preserve">ME_blue</t>
   </si>
   <si>
+    <t xml:space="preserve">ME_brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_green</t>
+  </si>
+  <si>
     <t xml:space="preserve">ME_greenyellow</t>
   </si>
   <si>
@@ -161,19 +167,16 @@
     <t xml:space="preserve">ME_pink</t>
   </si>
   <si>
+    <t xml:space="preserve">ME_purple</t>
+  </si>
+  <si>
     <t xml:space="preserve">ME_red</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_tan</t>
+    <t xml:space="preserve">ME_turquoise</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_purple</t>
+    <t xml:space="preserve">ME_yellow</t>
   </si>
 </sst>
 </file>
@@ -560,13 +563,13 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.599173971108695</v>
+        <v>-0.14795918367347</v>
       </c>
       <c r="I2" t="n">
         <v>-1</v>
@@ -593,28 +596,28 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.599173971108695</v>
+        <v>-0.14795918367347</v>
       </c>
       <c r="I3" t="n">
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.885572139303483</v>
+        <v>0.388059701492537</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.377853075698021</v>
+        <v>-0.929020358005425</v>
       </c>
       <c r="M3" t="n">
-        <v>0.860567518577484</v>
+        <v>2.84544642224662</v>
       </c>
     </row>
     <row r="4">
@@ -634,16 +637,16 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.821494867332811</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.996428571428571</v>
+        <v>-1</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -667,28 +670,28 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.821494867332811</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.996428571428571</v>
+        <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.90547263681592</v>
+        <v>0.228855721393035</v>
       </c>
       <c r="K5" t="n">
-        <v>0.552238805970149</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.44570140918943</v>
+        <v>-0.818716109210569</v>
       </c>
       <c r="M5" t="n">
-        <v>0.810087188568839</v>
+        <v>2.64182288983315</v>
       </c>
     </row>
     <row r="6">
@@ -708,13 +711,13 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.58072601412863</v>
       </c>
       <c r="I6" t="n">
         <v>-1</v>
@@ -741,28 +744,28 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.58072601412863</v>
       </c>
       <c r="I7" t="n">
         <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.432835820895522</v>
+        <v>0.955223880597015</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.332561842392412</v>
+        <v>-0.905896471575087</v>
       </c>
       <c r="M7" t="n">
-        <v>0.758779388900574</v>
+        <v>3.29162632854012</v>
       </c>
     </row>
     <row r="8">
@@ -782,16 +785,16 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.375804247363091</v>
+        <v>0.249732775292857</v>
       </c>
       <c r="I8" t="n">
-        <v>0.767857142857143</v>
+        <v>0.457142857142857</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -815,28 +818,28 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>0.375804247363091</v>
+        <v>0.249732775292857</v>
       </c>
       <c r="I9" t="n">
-        <v>0.767857142857143</v>
+        <v>0.457142857142857</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0099502487562189</v>
+        <v>0.0149253731343284</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0099502487562189</v>
+        <v>0.0348258706467662</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.366835038734925</v>
+        <v>-0.944401055961812</v>
       </c>
       <c r="M9" t="n">
-        <v>0.510183901140575</v>
+        <v>2.9143487690887</v>
       </c>
     </row>
     <row r="10">
@@ -856,16 +859,16 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.165341811931635</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.996415759077198</v>
+        <v>-0.929988041805385</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -889,28 +892,28 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.165341811931635</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.996415759077198</v>
+        <v>-0.929988041805385</v>
       </c>
       <c r="J11" t="n">
-        <v>0.223880597014925</v>
+        <v>0.497512437810945</v>
       </c>
       <c r="K11" t="n">
-        <v>0.666666666666667</v>
+        <v>0.358208955223881</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.34418981434806</v>
+        <v>-0.763429966900632</v>
       </c>
       <c r="M11" t="n">
-        <v>0.458968642714291</v>
+        <v>3.05403212485878</v>
       </c>
     </row>
     <row r="12">
@@ -930,13 +933,13 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.258251957365421</v>
       </c>
       <c r="I12" t="n">
         <v>-1</v>
@@ -963,28 +966,28 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.258251957365421</v>
       </c>
       <c r="I13" t="n">
         <v>-1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.343283582089552</v>
+        <v>0.537313432835821</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.439939587723883</v>
+        <v>-0.918859298947979</v>
       </c>
       <c r="M13" t="n">
-        <v>1.22770587116728</v>
+        <v>2.98870514125754</v>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.627805262922724</v>
+        <v>-1.36896623005527</v>
       </c>
     </row>
     <row r="3">
@@ -1028,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.159615458699803</v>
+        <v>-0.35702183283983</v>
       </c>
     </row>
     <row r="4">
@@ -1039,7 +1042,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.67986791577693</v>
       </c>
     </row>
     <row r="5">
@@ -1050,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.199452777160151</v>
       </c>
     </row>
     <row r="6">
@@ -1061,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.21185226805657</v>
+        <v>-0.294077902447707</v>
       </c>
     </row>
     <row r="7">
@@ -1072,7 +1075,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.41472321953108</v>
+        <v>-0.520764815029834</v>
       </c>
     </row>
     <row r="8">
@@ -1083,7 +1086,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.182626788863393</v>
+        <v>-0.263167599275821</v>
       </c>
     </row>
     <row r="9">
@@ -1094,7 +1097,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.36551208415823</v>
+        <v>-0.336047313895173</v>
       </c>
     </row>
     <row r="10">
@@ -1127,7 +1130,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.607822577102715</v>
       </c>
     </row>
     <row r="13">
@@ -1138,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.195049405438156</v>
+        <v>-0.260613110538829</v>
       </c>
     </row>
     <row r="14">
@@ -1149,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.223625252498942</v>
+        <v>-0.410465528116538</v>
       </c>
     </row>
     <row r="15">
@@ -1182,7 +1185,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.119602709622401</v>
+        <v>-0.151937106095553</v>
       </c>
     </row>
     <row r="18">
@@ -1193,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.415600554770831</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="19">
@@ -1204,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.251786395296702</v>
+        <v>-0.381883191388413</v>
       </c>
     </row>
     <row r="20">
@@ -1215,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.289999430297988</v>
+        <v>-1.65665551645879</v>
       </c>
     </row>
     <row r="21">
@@ -1226,7 +1229,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.454757997298332</v>
       </c>
     </row>
     <row r="22">
@@ -1237,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.453556978086726</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="23">
@@ -1248,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.356685837298232</v>
+        <v>-0.673492702837206</v>
       </c>
     </row>
     <row r="24">
@@ -1259,7 +1262,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.381215851073076</v>
+        <v>-5.58460033085496</v>
       </c>
     </row>
     <row r="25">
@@ -1281,7 +1284,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.40886750418649</v>
+        <v>0.467768986850973</v>
       </c>
     </row>
     <row r="27">
@@ -1303,7 +1306,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.243750719192957</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="29">
@@ -1314,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.194569771605431</v>
+        <v>-0.182693778696956</v>
       </c>
     </row>
     <row r="30">
@@ -1336,7 +1339,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.239745984479865</v>
+        <v>-0.341218414607144</v>
       </c>
     </row>
     <row r="32">
@@ -1369,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.381255751507299</v>
+        <v>-0.243684340095022</v>
       </c>
     </row>
     <row r="35">
@@ -1380,7 +1383,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.44230036143656</v>
+        <v>-0.371233661392914</v>
       </c>
     </row>
     <row r="36">
@@ -1391,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.144369920827217</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="37">
@@ -1435,7 +1438,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.159792131220689</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="41">
@@ -1446,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.211398478308261</v>
+        <v>-0.472731454538894</v>
       </c>
     </row>
     <row r="42">
@@ -1479,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.233258533181805</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="45">
@@ -1490,7 +1493,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.187777037369905</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="46">
@@ -1501,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.249485149216716</v>
       </c>
     </row>
     <row r="47">
@@ -1512,7 +1515,7 @@
         <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0642000258055457</v>
+        <v>-1.46482680511238</v>
       </c>
     </row>
     <row r="48">
@@ -1523,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.378616717005942</v>
+        <v>-0.267412420591947</v>
       </c>
     </row>
     <row r="49">
@@ -1534,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.492996684316734</v>
+        <v>-0.376075653647675</v>
       </c>
     </row>
     <row r="50">
@@ -1545,7 +1548,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-3.10411340408158</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="51">
@@ -1556,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.185376449015627</v>
+        <v>-0.225437029784675</v>
       </c>
     </row>
     <row r="52">
@@ -1567,7 +1570,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.191636921105224</v>
+        <v>-0.347950936121329</v>
       </c>
     </row>
     <row r="53">
@@ -1578,7 +1581,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.416581534469429</v>
+        <v>-0.693936842022283</v>
       </c>
     </row>
     <row r="54">
@@ -1589,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.29873508313601</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="55">
@@ -1600,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-1.54140171510417</v>
+        <v>-2.11164432407874</v>
       </c>
     </row>
     <row r="56">
@@ -1611,7 +1614,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.147959183673469</v>
+        <v>-4.19518968504612</v>
       </c>
     </row>
     <row r="57">
@@ -1622,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.331381069673599</v>
       </c>
     </row>
     <row r="58">
@@ -1633,7 +1636,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.172997785146112</v>
       </c>
     </row>
     <row r="59">
@@ -1644,7 +1647,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.15261951645792</v>
+        <v>-16.6493138048847</v>
       </c>
     </row>
     <row r="60">
@@ -1655,7 +1658,7 @@
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.225068957908225</v>
+        <v>-0.105419333148732</v>
       </c>
     </row>
     <row r="61">
@@ -1677,7 +1680,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-10.8198790984261</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="63">
@@ -1688,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.239410373452014</v>
+        <v>-1.6415967219439</v>
       </c>
     </row>
     <row r="64">
@@ -1699,7 +1702,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.393243419833838</v>
       </c>
     </row>
     <row r="65">
@@ -1721,7 +1724,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.159623860077861</v>
       </c>
     </row>
     <row r="67">
@@ -1732,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.204401360254896</v>
+        <v>-0.381628295068587</v>
       </c>
     </row>
     <row r="68">
@@ -1743,7 +1746,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.425424831556034</v>
       </c>
     </row>
     <row r="69">
@@ -1754,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.157956693222161</v>
+        <v>-0.479010497072098</v>
       </c>
     </row>
     <row r="70">
@@ -1765,7 +1768,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.242825674165501</v>
+        <v>-0.273053150667794</v>
       </c>
     </row>
     <row r="71">
@@ -1776,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.210189402593923</v>
+        <v>-3.0800974719323</v>
       </c>
     </row>
     <row r="72">
@@ -1787,7 +1790,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.267880902918765</v>
       </c>
     </row>
     <row r="73">
@@ -1798,7 +1801,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.431380532961597</v>
+        <v>-0.18238617036347</v>
       </c>
     </row>
     <row r="74">
@@ -1809,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.210419074917227</v>
+        <v>-0.549092079193629</v>
       </c>
     </row>
     <row r="75">
@@ -1831,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.187592718595269</v>
+        <v>-0.234538577005408</v>
       </c>
     </row>
     <row r="77">
@@ -1842,7 +1845,7 @@
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>0.248418409443534</v>
+        <v>0.102607101005617</v>
       </c>
     </row>
     <row r="78">
@@ -1853,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.988858300388076</v>
       </c>
     </row>
     <row r="79">
@@ -1875,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.260377098483423</v>
+        <v>-0.0981667491878466</v>
       </c>
     </row>
     <row r="81">
@@ -1886,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.302485244079546</v>
+        <v>0.0896235294625473</v>
       </c>
     </row>
     <row r="82">
@@ -1897,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.0331955568323046</v>
+        <v>-0.057072540516385</v>
       </c>
     </row>
     <row r="83">
@@ -1908,7 +1911,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-2.00020796315265</v>
+        <v>-0.224755154496947</v>
       </c>
     </row>
     <row r="84">
@@ -1919,7 +1922,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.295534996981762</v>
+        <v>-6.04538060317303</v>
       </c>
     </row>
     <row r="85">
@@ -1930,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.0787563845293728</v>
+        <v>-1.21734477439635</v>
       </c>
     </row>
     <row r="86">
@@ -1941,7 +1944,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.755736215727846</v>
       </c>
     </row>
     <row r="87">
@@ -1952,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.407227188403607</v>
+        <v>-0.222651011162574</v>
       </c>
     </row>
     <row r="88">
@@ -1963,7 +1966,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.981015825198518</v>
       </c>
     </row>
     <row r="89">
@@ -1974,7 +1977,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.819778532162754</v>
+        <v>-1.03981714585398</v>
       </c>
     </row>
     <row r="90">
@@ -1996,7 +1999,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.11809748858442</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="92">
@@ -2007,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.417778871181264</v>
+        <v>-1.48652180754806</v>
       </c>
     </row>
     <row r="93">
@@ -2018,7 +2021,7 @@
         <v>16</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.959360590353175</v>
+        <v>-1.1575104272527</v>
       </c>
     </row>
     <row r="94">
@@ -2040,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.354878659511773</v>
+        <v>0.0757291240376746</v>
       </c>
     </row>
     <row r="96">
@@ -2051,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.870099115587259</v>
+        <v>0.322305600402309</v>
       </c>
     </row>
     <row r="97">
@@ -2062,7 +2065,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.297289196743297</v>
+        <v>-0.222725979046643</v>
       </c>
     </row>
     <row r="98">
@@ -2073,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.17931181796993</v>
+        <v>-0.318152172969027</v>
       </c>
     </row>
     <row r="99">
@@ -2084,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.53267620763361</v>
       </c>
     </row>
     <row r="100">
@@ -2095,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.237827067566758</v>
+        <v>-0.37992502987876</v>
       </c>
     </row>
     <row r="101">
@@ -2106,7 +2109,7 @@
         <v>16</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.244486546314359</v>
+        <v>-0.639318539201554</v>
       </c>
     </row>
     <row r="102">
@@ -2117,7 +2120,7 @@
         <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.429233222229283</v>
+        <v>-12.1794332355076</v>
       </c>
     </row>
     <row r="103">
@@ -2128,7 +2131,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.684385446044613</v>
+        <v>-0.756142425095796</v>
       </c>
     </row>
     <row r="104">
@@ -2150,7 +2153,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.329023784941113</v>
+        <v>0.0562406724877053</v>
       </c>
     </row>
     <row r="106">
@@ -2161,7 +2164,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.107930410593774</v>
+        <v>0.149574944780729</v>
       </c>
     </row>
     <row r="107">
@@ -2172,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.220131995178646</v>
+        <v>-0.595108379757682</v>
       </c>
     </row>
     <row r="108">
@@ -2183,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.466436983220765</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="109">
@@ -2194,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>0.307106457662343</v>
+        <v>-0.569781604808012</v>
       </c>
     </row>
     <row r="110">
@@ -2205,7 +2208,7 @@
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.387198711134006</v>
       </c>
     </row>
     <row r="111">
@@ -2216,7 +2219,7 @@
         <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.222291472611775</v>
+        <v>-24.3834040192155</v>
       </c>
     </row>
     <row r="112">
@@ -2227,7 +2230,7 @@
         <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0764954037119739</v>
+        <v>-0.886969459203643</v>
       </c>
     </row>
     <row r="113">
@@ -2260,7 +2263,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.772133545143079</v>
+        <v>-0.20032106033666</v>
       </c>
     </row>
     <row r="116">
@@ -2271,7 +2274,7 @@
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.225851454705203</v>
       </c>
     </row>
     <row r="117">
@@ -2282,7 +2285,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.494807033985101</v>
+        <v>-0.305409972787645</v>
       </c>
     </row>
     <row r="118">
@@ -2293,7 +2296,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.152145355881328</v>
+        <v>-1.05223637264681</v>
       </c>
     </row>
     <row r="119">
@@ -2315,7 +2318,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.199369771075817</v>
+        <v>-0.29108949274119</v>
       </c>
     </row>
     <row r="121">
@@ -2326,7 +2329,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.600240422752863</v>
       </c>
     </row>
     <row r="122">
@@ -2337,7 +2340,7 @@
         <v>16</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.299074380004098</v>
+        <v>-0.285347646031171</v>
       </c>
     </row>
     <row r="123">
@@ -2359,7 +2362,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.2409208960012</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="125">
@@ -2370,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.105922058015944</v>
       </c>
     </row>
     <row r="126">
@@ -2381,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.176945429399073</v>
+        <v>-0.182470955325972</v>
       </c>
     </row>
     <row r="127">
@@ -2392,7 +2395,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.161534942631987</v>
+        <v>-0.547175539514077</v>
       </c>
     </row>
     <row r="128">
@@ -2403,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.660822420086305</v>
       </c>
     </row>
     <row r="129">
@@ -2414,7 +2417,7 @@
         <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>-2.20003357390155</v>
+        <v>-4.54819646332605</v>
       </c>
     </row>
     <row r="130">
@@ -2425,7 +2428,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.842133289678321</v>
+        <v>-0.035891366884742</v>
       </c>
     </row>
     <row r="131">
@@ -2447,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.222189981300183</v>
+        <v>-0.776066138603559</v>
       </c>
     </row>
     <row r="133">
@@ -2469,7 +2472,7 @@
         <v>16</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.14795918367347</v>
+        <v>-3.53567823435112</v>
       </c>
     </row>
     <row r="135">
@@ -2480,7 +2483,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.563049389368558</v>
       </c>
     </row>
     <row r="136">
@@ -2491,7 +2494,7 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.250332151002343</v>
+        <v>-0.29715509058284</v>
       </c>
     </row>
     <row r="137">
@@ -2502,7 +2505,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.692143860024917</v>
       </c>
     </row>
     <row r="138">
@@ -2513,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.0877628065469429</v>
+        <v>-0.4291058317752</v>
       </c>
     </row>
     <row r="139">
@@ -2557,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.277621801940181</v>
+        <v>-0.567807847497377</v>
       </c>
     </row>
     <row r="143">
@@ -2568,7 +2571,7 @@
         <v>16</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.131189415936647</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="144">
@@ -2590,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.609442775829597</v>
+        <v>-0.911307427242406</v>
       </c>
     </row>
     <row r="146">
@@ -2601,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.742675265229469</v>
+        <v>-0.333037989957047</v>
       </c>
     </row>
     <row r="147">
@@ -2612,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.960669963836081</v>
+        <v>-0.238101212057355</v>
       </c>
     </row>
     <row r="148">
@@ -2623,7 +2626,7 @@
         <v>16</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.399913134414322</v>
       </c>
     </row>
     <row r="149">
@@ -2634,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.421148345647487</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="150">
@@ -2667,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.0991739229586739</v>
+        <v>-0.902295502663894</v>
       </c>
     </row>
     <row r="153">
@@ -2678,7 +2681,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.254756669360445</v>
+        <v>-0.222825772751081</v>
       </c>
     </row>
     <row r="154">
@@ -2689,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.259444828410362</v>
+        <v>-3.63748026119313</v>
       </c>
     </row>
     <row r="155">
@@ -2700,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.49639007617668</v>
+        <v>-0.295412535334069</v>
       </c>
     </row>
     <row r="156">
@@ -2711,7 +2714,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.353248496476676</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="157">
@@ -2722,7 +2725,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>0.39842917349591</v>
+        <v>-1.05048043286379</v>
       </c>
     </row>
     <row r="158">
@@ -2733,7 +2736,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.212071826846192</v>
+        <v>-0.383604563061961</v>
       </c>
     </row>
     <row r="159">
@@ -2777,7 +2780,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>-1.40507364565677</v>
+        <v>-0.275201316913342</v>
       </c>
     </row>
     <row r="163">
@@ -2788,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.237994544144534</v>
+        <v>-1.94528435978214</v>
       </c>
     </row>
     <row r="164">
@@ -2810,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.23531611376834</v>
+        <v>-0.93481305148591</v>
       </c>
     </row>
     <row r="166">
@@ -2832,7 +2835,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.236555158597892</v>
       </c>
     </row>
     <row r="168">
@@ -2843,7 +2846,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.599559871996316</v>
+        <v>-0.573868570938198</v>
       </c>
     </row>
     <row r="169">
@@ -2854,7 +2857,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>-1.96329027504384</v>
+        <v>-0.217467816986664</v>
       </c>
     </row>
     <row r="170">
@@ -2876,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.173580023842963</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="172">
@@ -2887,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>-1.95187473752279</v>
+        <v>-23.3611850250165</v>
       </c>
     </row>
     <row r="173">
@@ -2898,7 +2901,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.153732462017812</v>
+        <v>-1.73638351140372</v>
       </c>
     </row>
     <row r="174">
@@ -2909,7 +2912,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.158897669611783</v>
+        <v>-0.437645507762255</v>
       </c>
     </row>
     <row r="175">
@@ -2931,7 +2934,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.495895248786451</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="177">
@@ -2942,7 +2945,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.199682650473414</v>
+        <v>-0.219418508834766</v>
       </c>
     </row>
     <row r="178">
@@ -2964,7 +2967,7 @@
         <v>16</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.156810561378986</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="180">
@@ -2975,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.333515892767584</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="181">
@@ -2986,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.345597653104349</v>
+        <v>-0.837558966558993</v>
       </c>
     </row>
     <row r="182">
@@ -2997,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-1.68713214886153</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="183">
@@ -3008,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.30561226045203</v>
+        <v>-0.447996822306476</v>
       </c>
     </row>
     <row r="184">
@@ -3019,7 +3022,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.196848447138479</v>
+        <v>-0.194575694191536</v>
       </c>
     </row>
     <row r="185">
@@ -3030,7 +3033,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.0492089667836015</v>
+        <v>0.192083223254758</v>
       </c>
     </row>
     <row r="186">
@@ -3041,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.456537469965582</v>
+        <v>-1.83433951161919</v>
       </c>
     </row>
     <row r="187">
@@ -3052,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.346538829800674</v>
+        <v>-0.497331711012987</v>
       </c>
     </row>
     <row r="188">
@@ -3063,7 +3066,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.400936172837063</v>
+        <v>-0.501583922966933</v>
       </c>
     </row>
     <row r="189">
@@ -3074,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.0657628678235178</v>
+        <v>-1.8780800641392</v>
       </c>
     </row>
     <row r="190">
@@ -3085,7 +3088,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.555778888947061</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="191">
@@ -3096,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.783030393004011</v>
+        <v>-0.708096794253547</v>
       </c>
     </row>
     <row r="192">
@@ -3107,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.148175672265399</v>
+        <v>-0.309363663446767</v>
       </c>
     </row>
     <row r="193">
@@ -3118,7 +3121,7 @@
         <v>16</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.68570574394992</v>
       </c>
     </row>
     <row r="194">
@@ -3129,7 +3132,7 @@
         <v>16</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.258576958948937</v>
+        <v>-0.210015981064402</v>
       </c>
     </row>
     <row r="195">
@@ -3140,7 +3143,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.194318743140057</v>
       </c>
     </row>
     <row r="196">
@@ -3151,7 +3154,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>-2.4820367597539</v>
+        <v>-1.62300000848324</v>
       </c>
     </row>
     <row r="197">
@@ -3173,7 +3176,7 @@
         <v>16</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.310208478524057</v>
       </c>
     </row>
     <row r="199">
@@ -3184,7 +3187,7 @@
         <v>16</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.41622284711494</v>
       </c>
     </row>
     <row r="200">
@@ -3195,7 +3198,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.582526384235283</v>
       </c>
     </row>
     <row r="201">
@@ -3217,7 +3220,7 @@
         <v>16</v>
       </c>
       <c r="C202" t="n">
-        <v>-2.36571562039007</v>
+        <v>-0.307769290167565</v>
       </c>
     </row>
     <row r="203">
@@ -3228,7 +3231,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.408873516061318</v>
+        <v>0.00577932433026629</v>
       </c>
     </row>
     <row r="204">
@@ -3239,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.114384315352538</v>
+        <v>-4.67828955647939</v>
       </c>
     </row>
     <row r="205">
@@ -3261,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.25295188850359</v>
+        <v>-0.34694603986721</v>
       </c>
     </row>
     <row r="207">
@@ -3272,7 +3275,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.169549592438474</v>
+        <v>-0.758392910919635</v>
       </c>
     </row>
     <row r="208">
@@ -3283,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.205912732893866</v>
+        <v>-0.268540697373699</v>
       </c>
     </row>
     <row r="209">
@@ -3294,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.492822367856406</v>
+        <v>-0.50861036393131</v>
       </c>
     </row>
     <row r="210">
@@ -3316,7 +3319,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.459965718649991</v>
+        <v>-0.398557732551202</v>
       </c>
     </row>
     <row r="212">
@@ -3327,7 +3330,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.09808904665411</v>
       </c>
     </row>
     <row r="213">
@@ -3338,7 +3341,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.204528310653224</v>
+        <v>-2.16858924959145</v>
       </c>
     </row>
     <row r="214">
@@ -3349,7 +3352,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.225570448530191</v>
+        <v>-0.268644308923187</v>
       </c>
     </row>
     <row r="215">
@@ -3371,7 +3374,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-2.27261443900167</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="217">
@@ -3393,7 +3396,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.478840906155889</v>
+        <v>-0.352388602628485</v>
       </c>
     </row>
     <row r="219">
@@ -3404,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.349992580415044</v>
+        <v>-0.810806579906945</v>
       </c>
     </row>
     <row r="220">
@@ -3426,7 +3429,7 @@
         <v>16</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.786232381442955</v>
+        <v>0.207004771609712</v>
       </c>
     </row>
     <row r="222">
@@ -3448,7 +3451,7 @@
         <v>16</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.190836762592348</v>
+        <v>-0.0541099443472319</v>
       </c>
     </row>
     <row r="224">
@@ -3459,7 +3462,7 @@
         <v>16</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.14795918367347</v>
+        <v>-5.60874377085273</v>
       </c>
     </row>
     <row r="225">
@@ -3470,7 +3473,7 @@
         <v>16</v>
       </c>
       <c r="C225" t="n">
-        <v>-1.14406004067427</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="226">
@@ -3481,7 +3484,7 @@
         <v>16</v>
       </c>
       <c r="C226" t="n">
-        <v>-1.93689141496494</v>
+        <v>-0.127166169379227</v>
       </c>
     </row>
     <row r="227">
@@ -3514,7 +3517,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.343156797997562</v>
+        <v>-0.291058433360017</v>
       </c>
     </row>
     <row r="230">
@@ -3536,7 +3539,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.135235418557836</v>
+        <v>0.267133484507733</v>
       </c>
     </row>
     <row r="232">
@@ -3569,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.300514203429781</v>
+        <v>-0.344754478479193</v>
       </c>
     </row>
     <row r="235">
@@ -3580,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.383072155591776</v>
+        <v>-0.496378585961905</v>
       </c>
     </row>
     <row r="236">
@@ -3591,7 +3594,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.470850241481081</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="237">
@@ -3602,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.175438913586362</v>
+        <v>-1.32363254387455</v>
       </c>
     </row>
     <row r="238">
@@ -3646,7 +3649,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.233434073887262</v>
+        <v>-0.338430797221859</v>
       </c>
     </row>
     <row r="242">
@@ -3657,7 +3660,7 @@
         <v>16</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.144771034335369</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="243">
@@ -3679,7 +3682,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.292664337414521</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="245">
@@ -3690,7 +3693,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.174549440215759</v>
       </c>
     </row>
     <row r="246">
@@ -3701,7 +3704,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.421963087167858</v>
+        <v>-0.376042394101273</v>
       </c>
     </row>
     <row r="247">
@@ -3712,7 +3715,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.301553185310721</v>
+        <v>-0.7273684780488</v>
       </c>
     </row>
     <row r="248">
@@ -3723,7 +3726,7 @@
         <v>16</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.258756260506558</v>
+        <v>-0.154558409413948</v>
       </c>
     </row>
     <row r="249">
@@ -3734,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.403289697995872</v>
+        <v>-0.367612702968285</v>
       </c>
     </row>
     <row r="250">
@@ -3756,7 +3759,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.688435569883125</v>
+        <v>-0.440283109217679</v>
       </c>
     </row>
     <row r="252">
@@ -3767,7 +3770,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.19996813613143</v>
       </c>
     </row>
     <row r="253">
@@ -3789,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.737436006981797</v>
+        <v>-0.418612740477281</v>
       </c>
     </row>
     <row r="255">
@@ -3811,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-4.57610626416275</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="257">
@@ -3833,7 +3836,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.194271062445314</v>
+        <v>-0.0264042622008369</v>
       </c>
     </row>
     <row r="259">
@@ -3844,7 +3847,7 @@
         <v>16</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.57113741556705</v>
+        <v>-0.385931505425326</v>
       </c>
     </row>
     <row r="260">
@@ -3855,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.267490785678872</v>
+        <v>-0.162911380498791</v>
       </c>
     </row>
     <row r="261">
@@ -3888,7 +3891,7 @@
         <v>16</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.236151796834318</v>
+        <v>-0.35581204722417</v>
       </c>
     </row>
     <row r="264">
@@ -3899,7 +3902,7 @@
         <v>16</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.641355432822122</v>
+        <v>-0.400776841873577</v>
       </c>
     </row>
     <row r="265">
@@ -3910,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.433181844577084</v>
+        <v>-0.2686643440715</v>
       </c>
     </row>
     <row r="266">
@@ -3921,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.42706566897367</v>
+        <v>-5.75068413193143</v>
       </c>
     </row>
     <row r="267">
@@ -3932,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.392547048245579</v>
+        <v>-0.757276152439496</v>
       </c>
     </row>
     <row r="268">
@@ -3943,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.347191168194672</v>
+        <v>-0.389556441967033</v>
       </c>
     </row>
     <row r="269">
@@ -3954,7 +3957,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="n">
-        <v>-4.34349029768383</v>
+        <v>-0.989132199157202</v>
       </c>
     </row>
     <row r="270">
@@ -3965,7 +3968,7 @@
         <v>16</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.613453419520822</v>
+        <v>-1.24137658669648</v>
       </c>
     </row>
     <row r="271">
@@ -3987,7 +3990,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.582819955554972</v>
       </c>
     </row>
     <row r="273">
@@ -3998,7 +4001,7 @@
         <v>16</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.42388377562249</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="274">
@@ -4009,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.16675891034399</v>
+        <v>-0.182411417613522</v>
       </c>
     </row>
     <row r="275">
@@ -4031,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.04498838287421</v>
       </c>
     </row>
     <row r="277">
@@ -4075,7 +4078,7 @@
         <v>16</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.176677993084702</v>
+        <v>-0.136028906102646</v>
       </c>
     </row>
     <row r="281">
@@ -4086,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>0.0569815575039961</v>
+        <v>0.42219273683325</v>
       </c>
     </row>
     <row r="282">
@@ -4097,7 +4100,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="n">
-        <v>0.213172246450521</v>
+        <v>-0.00220699502938482</v>
       </c>
     </row>
     <row r="283">
@@ -4108,7 +4111,7 @@
         <v>16</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.183888184975396</v>
+        <v>-0.331354863455567</v>
       </c>
     </row>
     <row r="284">
@@ -4130,7 +4133,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-1.66525463043953</v>
+        <v>-0.368844889059093</v>
       </c>
     </row>
     <row r="286">
@@ -4141,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.439112758906681</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="287">
@@ -4152,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.598794234294827</v>
+        <v>-0.974776399856822</v>
       </c>
     </row>
     <row r="288">
@@ -4163,7 +4166,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="n">
-        <v>-2.13505267059521</v>
+        <v>-15.3591450268928</v>
       </c>
     </row>
     <row r="289">
@@ -4174,7 +4177,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.357822077936939</v>
       </c>
     </row>
     <row r="290">
@@ -4185,7 +4188,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-1.5274032315755</v>
+        <v>-0.477904139314743</v>
       </c>
     </row>
     <row r="291">
@@ -4196,7 +4199,7 @@
         <v>16</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.416484914979574</v>
+        <v>-0.371407074485107</v>
       </c>
     </row>
     <row r="292">
@@ -4207,7 +4210,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.31757500257298</v>
+        <v>-0.217313715738791</v>
       </c>
     </row>
     <row r="293">
@@ -4218,7 +4221,7 @@
         <v>16</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.664995130259196</v>
+        <v>-0.716008467149322</v>
       </c>
     </row>
     <row r="294">
@@ -4229,7 +4232,7 @@
         <v>16</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.147959183673469</v>
+        <v>-14.1354069852399</v>
       </c>
     </row>
     <row r="295">
@@ -4240,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.151232841882823</v>
       </c>
     </row>
     <row r="296">
@@ -4251,7 +4254,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.286260362780109</v>
+        <v>-1.05701946375257</v>
       </c>
     </row>
     <row r="297">
@@ -4273,7 +4276,7 @@
         <v>16</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.282033736267589</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="299">
@@ -4284,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.94027224769286</v>
       </c>
     </row>
     <row r="300">
@@ -4295,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.41637570715148</v>
+        <v>-0.217848217475091</v>
       </c>
     </row>
     <row r="301">
@@ -4306,7 +4309,7 @@
         <v>16</v>
       </c>
       <c r="C301" t="n">
-        <v>-1.19185845171417</v>
+        <v>-1.49048846024104</v>
       </c>
     </row>
     <row r="302">
@@ -4317,7 +4320,7 @@
         <v>16</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.403675223487821</v>
+        <v>-0.976427729172964</v>
       </c>
     </row>
     <row r="303">
@@ -4328,7 +4331,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.594244425011992</v>
+        <v>-1.35992659302625</v>
       </c>
     </row>
     <row r="304">
@@ -4339,7 +4342,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.40991410773194</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="305">
@@ -4350,7 +4353,7 @@
         <v>16</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.136486184067788</v>
+        <v>-0.126756904085482</v>
       </c>
     </row>
     <row r="306">
@@ -4361,7 +4364,7 @@
         <v>16</v>
       </c>
       <c r="C306" t="n">
-        <v>0.32513536841782</v>
+        <v>0.338555907951136</v>
       </c>
     </row>
     <row r="307">
@@ -4372,7 +4375,7 @@
         <v>16</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.363042946163265</v>
+        <v>-0.664989941566013</v>
       </c>
     </row>
     <row r="308">
@@ -4383,7 +4386,7 @@
         <v>16</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.284293828524266</v>
+        <v>-4.24383333133198</v>
       </c>
     </row>
     <row r="309">
@@ -4394,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.358467249624875</v>
+        <v>0.942195868577439</v>
       </c>
     </row>
     <row r="310">
@@ -4416,7 +4419,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.285428411143295</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="312">
@@ -4427,7 +4430,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.195312713870885</v>
+        <v>-0.183986463676007</v>
       </c>
     </row>
     <row r="313">
@@ -4438,7 +4441,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.196968719886809</v>
       </c>
     </row>
     <row r="314">
@@ -4449,7 +4452,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.164543912355672</v>
+        <v>-0.173788743468891</v>
       </c>
     </row>
     <row r="315">
@@ -4460,7 +4463,7 @@
         <v>16</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.771202031831355</v>
+        <v>-1.07580027544883</v>
       </c>
     </row>
     <row r="316">
@@ -4471,7 +4474,7 @@
         <v>16</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.413118587017919</v>
+        <v>-0.237092642009759</v>
       </c>
     </row>
     <row r="317">
@@ -4482,7 +4485,7 @@
         <v>16</v>
       </c>
       <c r="C317" t="n">
-        <v>-0.549500428113567</v>
+        <v>-0.248701806513064</v>
       </c>
     </row>
     <row r="318">
@@ -4504,7 +4507,7 @@
         <v>16</v>
       </c>
       <c r="C319" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.323583872732488</v>
       </c>
     </row>
     <row r="320">
@@ -4515,7 +4518,7 @@
         <v>16</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.810100191064016</v>
       </c>
     </row>
     <row r="321">
@@ -4537,7 +4540,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.283105076874972</v>
+        <v>-0.520987162141312</v>
       </c>
     </row>
     <row r="323">
@@ -4559,7 +4562,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.06212903869088</v>
       </c>
     </row>
     <row r="325">
@@ -4581,7 +4584,7 @@
         <v>16</v>
       </c>
       <c r="C326" t="n">
-        <v>-0.378771815707391</v>
+        <v>-21.4067150000473</v>
       </c>
     </row>
     <row r="327">
@@ -4592,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.321670796707935</v>
+        <v>-0.16191081034766</v>
       </c>
     </row>
     <row r="328">
@@ -4603,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.754419430801579</v>
+        <v>-0.106497811749286</v>
       </c>
     </row>
     <row r="329">
@@ -4614,7 +4617,7 @@
         <v>16</v>
       </c>
       <c r="C329" t="n">
-        <v>-0.783027126708497</v>
+        <v>-0.877158518644484</v>
       </c>
     </row>
     <row r="330">
@@ -4625,7 +4628,7 @@
         <v>16</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.930238623955771</v>
+        <v>-0.788121962167778</v>
       </c>
     </row>
     <row r="331">
@@ -4647,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.0369191500148629</v>
+        <v>-0.263888884048159</v>
       </c>
     </row>
     <row r="333">
@@ -4669,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.949382163172519</v>
       </c>
     </row>
     <row r="335">
@@ -4680,7 +4683,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.222786216881967</v>
+        <v>-0.0479881639800588</v>
       </c>
     </row>
     <row r="336">
@@ -4691,7 +4694,7 @@
         <v>16</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.379924962624008</v>
       </c>
     </row>
     <row r="337">
@@ -4713,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.0369280909309027</v>
+        <v>0.0743532175528483</v>
       </c>
     </row>
     <row r="339">
@@ -4724,7 +4727,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.562790153433094</v>
+        <v>-3.13038429405232</v>
       </c>
     </row>
     <row r="340">
@@ -4746,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.40760902675675</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="342">
@@ -4757,7 +4760,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.488048955860696</v>
       </c>
     </row>
     <row r="343">
@@ -4768,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.894882616513848</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="344">
@@ -4779,7 +4782,7 @@
         <v>16</v>
       </c>
       <c r="C344" t="n">
-        <v>-0.230281000875514</v>
+        <v>-0.777576757442894</v>
       </c>
     </row>
     <row r="345">
@@ -4790,7 +4793,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>0.460167191618812</v>
+        <v>0.53900609951366</v>
       </c>
     </row>
     <row r="346">
@@ -4801,7 +4804,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>-4.81106624947285</v>
+        <v>-1.58495333439211</v>
       </c>
     </row>
     <row r="347">
@@ -4823,7 +4826,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.292573976657156</v>
+        <v>-0.337755829585166</v>
       </c>
     </row>
     <row r="349">
@@ -4834,7 +4837,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>0.0360788618764469</v>
+        <v>-0.362547463380356</v>
       </c>
     </row>
     <row r="350">
@@ -4856,7 +4859,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.342888229749315</v>
+        <v>-0.639701491308668</v>
       </c>
     </row>
     <row r="352">
@@ -4867,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.240490769661273</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="353">
@@ -4878,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.195939736339049</v>
+        <v>-0.520998518572529</v>
       </c>
     </row>
     <row r="354">
@@ -4889,7 +4892,7 @@
         <v>16</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.196934037164407</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="355">
@@ -4900,7 +4903,7 @@
         <v>16</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.373885843475692</v>
       </c>
     </row>
     <row r="356">
@@ -4911,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.157435126279093</v>
       </c>
     </row>
     <row r="357">
@@ -4922,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>0.582931423554275</v>
+        <v>-0.287742125320205</v>
       </c>
     </row>
     <row r="358">
@@ -4955,7 +4958,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.210551000470472</v>
+        <v>-1.03297931317393</v>
       </c>
     </row>
     <row r="361">
@@ -4966,7 +4969,7 @@
         <v>16</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.211494782289627</v>
       </c>
     </row>
     <row r="362">
@@ -4977,7 +4980,7 @@
         <v>16</v>
       </c>
       <c r="C362" t="n">
-        <v>-1.61282371430516</v>
+        <v>-0.242957597833053</v>
       </c>
     </row>
     <row r="363">
@@ -4988,7 +4991,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.350936081408416</v>
+        <v>-0.287808450025547</v>
       </c>
     </row>
     <row r="364">
@@ -5010,7 +5013,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.45560732770652</v>
+        <v>-0.990655981882141</v>
       </c>
     </row>
     <row r="366">
@@ -5021,7 +5024,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.648011380747241</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="367">
@@ -5043,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.270690013971845</v>
+        <v>-0.210812176474604</v>
       </c>
     </row>
     <row r="369">
@@ -5054,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.294159553799817</v>
+        <v>-0.457801074618921</v>
       </c>
     </row>
     <row r="370">
@@ -5065,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.212690673449105</v>
+        <v>-0.191169721475694</v>
       </c>
     </row>
     <row r="371">
@@ -5076,7 +5079,7 @@
         <v>16</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.252472056964126</v>
+        <v>-1.23361388948491</v>
       </c>
     </row>
     <row r="372">
@@ -5109,7 +5112,7 @@
         <v>16</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.155203369970954</v>
+        <v>-0.0756740822853277</v>
       </c>
     </row>
     <row r="375">
@@ -5164,7 +5167,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.147959183673469</v>
+        <v>-21.2621589910602</v>
       </c>
     </row>
     <row r="380">
@@ -5175,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-1.7518241543276</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="381">
@@ -5208,7 +5211,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.158351367633118</v>
+        <v>-0.396319661518224</v>
       </c>
     </row>
     <row r="384">
@@ -5230,7 +5233,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>0.00507059904538287</v>
+        <v>0.189050022911256</v>
       </c>
     </row>
     <row r="386">
@@ -5241,7 +5244,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-6.16569383328654</v>
+        <v>-1.88061325388099</v>
       </c>
     </row>
     <row r="387">
@@ -5252,7 +5255,7 @@
         <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>-1.49360572120277</v>
+        <v>-0.190745636576604</v>
       </c>
     </row>
     <row r="388">
@@ -5263,7 +5266,7 @@
         <v>16</v>
       </c>
       <c r="C388" t="n">
-        <v>-0.270178315445732</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="389">
@@ -5274,7 +5277,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.0563192842499494</v>
+        <v>-0.624382299934048</v>
       </c>
     </row>
     <row r="390">
@@ -5285,7 +5288,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.873586441336443</v>
+        <v>-2.15146330348749</v>
       </c>
     </row>
     <row r="391">
@@ -5296,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.241484174934456</v>
+        <v>0.127446395459513</v>
       </c>
     </row>
     <row r="392">
@@ -5307,7 +5310,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.228237429363818</v>
+        <v>0.0291058536348479</v>
       </c>
     </row>
     <row r="393">
@@ -5318,7 +5321,7 @@
         <v>16</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.28596516707039</v>
+        <v>-0.417455565367628</v>
       </c>
     </row>
     <row r="394">
@@ -5329,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.325021908432334</v>
+        <v>-0.372976501270853</v>
       </c>
     </row>
     <row r="395">
@@ -5340,7 +5343,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>-0.167680668740338</v>
+        <v>-0.145049125735242</v>
       </c>
     </row>
     <row r="396">
@@ -5351,7 +5354,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.595901338535464</v>
+        <v>-0.367890282536093</v>
       </c>
     </row>
     <row r="397">
@@ -5362,7 +5365,7 @@
         <v>16</v>
       </c>
       <c r="C397" t="n">
-        <v>-3.87479825647407</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="398">
@@ -5373,7 +5376,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-0.411624858064472</v>
+        <v>-1.51166738875474</v>
       </c>
     </row>
     <row r="399">
@@ -5384,7 +5387,7 @@
         <v>16</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.220744123826302</v>
+        <v>-0.727923672021261</v>
       </c>
     </row>
     <row r="400">
@@ -5417,7 +5420,7 @@
         <v>16</v>
       </c>
       <c r="C402" t="n">
-        <v>-0.147959183673469</v>
+        <v>-4.70734898754968</v>
       </c>
     </row>
     <row r="403">
@@ -5428,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="C403" t="n">
-        <v>-0.196734024876681</v>
+        <v>-0.14333480605812</v>
       </c>
     </row>
     <row r="404">
@@ -5439,7 +5442,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.0866517220235172</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="405">
@@ -5461,7 +5464,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.211868538986997</v>
       </c>
     </row>
     <row r="407">
@@ -5472,7 +5475,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.69806547618133</v>
       </c>
     </row>
     <row r="408">
@@ -5483,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>0.0457866843658401</v>
+        <v>-0.0518694986171149</v>
       </c>
     </row>
     <row r="409">
@@ -5494,7 +5497,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="n">
-        <v>-0.349249623421492</v>
+        <v>-0.152147192192619</v>
       </c>
     </row>
     <row r="410">
@@ -5516,7 +5519,7 @@
         <v>16</v>
       </c>
       <c r="C411" t="n">
-        <v>-0.484542471166381</v>
+        <v>-0.488349876748933</v>
       </c>
     </row>
     <row r="412">
@@ -5527,7 +5530,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.4807489562584</v>
       </c>
     </row>
     <row r="413">
@@ -5538,7 +5541,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.157300700700553</v>
+        <v>-0.493426562510134</v>
       </c>
     </row>
     <row r="414">
@@ -5549,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-0.176632977199333</v>
+        <v>-0.210570234895391</v>
       </c>
     </row>
     <row r="415">
@@ -5560,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.17290933090789</v>
+        <v>-0.193536044392175</v>
       </c>
     </row>
     <row r="416">
@@ -5582,7 +5585,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.3984895987975</v>
       </c>
     </row>
     <row r="418">
@@ -5593,7 +5596,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.225432846181405</v>
+        <v>-0.412592338071825</v>
       </c>
     </row>
     <row r="419">
@@ -5604,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.0892848177716381</v>
+        <v>-1.43570887747567</v>
       </c>
     </row>
     <row r="420">
@@ -5615,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>-0.267873209476124</v>
+        <v>-0.239628497457125</v>
       </c>
     </row>
     <row r="421">
@@ -5626,7 +5629,7 @@
         <v>16</v>
       </c>
       <c r="C421" t="n">
-        <v>-0.385082689061136</v>
+        <v>-0.280872210158538</v>
       </c>
     </row>
     <row r="422">
@@ -5648,7 +5651,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.42422837601086</v>
+        <v>-0.56995336860382</v>
       </c>
     </row>
     <row r="424">
@@ -5659,7 +5662,7 @@
         <v>16</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.244593587071062</v>
       </c>
     </row>
     <row r="425">
@@ -5670,7 +5673,7 @@
         <v>16</v>
       </c>
       <c r="C425" t="n">
-        <v>-1.72779145281737</v>
+        <v>-19.5965774722442</v>
       </c>
     </row>
     <row r="426">
@@ -5681,7 +5684,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>-2.31222306621769</v>
+        <v>-0.16402350380917</v>
       </c>
     </row>
     <row r="427">
@@ -5703,7 +5706,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.396506867372086</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="429">
@@ -5714,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.271471796847187</v>
+        <v>-0.285760492958198</v>
       </c>
     </row>
     <row r="430">
@@ -5736,7 +5739,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>-0.307154680538995</v>
+        <v>-0.136377364429516</v>
       </c>
     </row>
     <row r="432">
@@ -5769,7 +5772,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.600309125670683</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="435">
@@ -5780,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.287873961254983</v>
       </c>
     </row>
     <row r="436">
@@ -5791,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.261054400664061</v>
+        <v>-0.258071545141674</v>
       </c>
     </row>
     <row r="437">
@@ -5802,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>-0.568868405615915</v>
+        <v>-0.141515913929673</v>
       </c>
     </row>
     <row r="438">
@@ -5846,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.173360665439853</v>
+        <v>-0.13333893405416</v>
       </c>
     </row>
     <row r="442">
@@ -5879,7 +5882,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.512727529192461</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="445">
@@ -5890,7 +5893,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.302916730062452</v>
+        <v>-0.35752758524724</v>
       </c>
     </row>
     <row r="446">
@@ -5901,7 +5904,7 @@
         <v>16</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.509924787136163</v>
+        <v>-0.164838874894238</v>
       </c>
     </row>
     <row r="447">
@@ -5912,7 +5915,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.181453305875127</v>
+        <v>-0.311800310772323</v>
       </c>
     </row>
     <row r="448">
@@ -5923,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="C448" t="n">
-        <v>-0.461177549418371</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="449">
@@ -5934,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.609652216908708</v>
+        <v>-0.987978070512351</v>
       </c>
     </row>
     <row r="450">
@@ -5989,7 +5992,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.422514810238949</v>
+        <v>-0.342729997781519</v>
       </c>
     </row>
     <row r="455">
@@ -6000,7 +6003,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.758044510792389</v>
       </c>
     </row>
     <row r="456">
@@ -6011,7 +6014,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.902681594329456</v>
       </c>
     </row>
     <row r="457">
@@ -6022,7 +6025,7 @@
         <v>16</v>
       </c>
       <c r="C457" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.447325022503853</v>
       </c>
     </row>
     <row r="458">
@@ -6033,7 +6036,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.179542765222834</v>
+        <v>-0.416766754145479</v>
       </c>
     </row>
     <row r="459">
@@ -6044,7 +6047,7 @@
         <v>16</v>
       </c>
       <c r="C459" t="n">
-        <v>-0.173838716737346</v>
+        <v>-0.328071362196859</v>
       </c>
     </row>
     <row r="460">
@@ -6055,7 +6058,7 @@
         <v>16</v>
       </c>
       <c r="C460" t="n">
-        <v>-0.415613949649288</v>
+        <v>-0.397574234671197</v>
       </c>
     </row>
     <row r="461">
@@ -6066,7 +6069,7 @@
         <v>16</v>
       </c>
       <c r="C461" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.185529800794646</v>
       </c>
     </row>
     <row r="462">
@@ -6088,7 +6091,7 @@
         <v>16</v>
       </c>
       <c r="C463" t="n">
-        <v>-0.208248728771599</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="464">
@@ -6099,7 +6102,7 @@
         <v>16</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.801544948165639</v>
+        <v>-0.457983465506328</v>
       </c>
     </row>
     <row r="465">
@@ -6121,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.804452778388405</v>
+        <v>-0.481652609756394</v>
       </c>
     </row>
     <row r="467">
@@ -6132,7 +6135,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-0.371833763752434</v>
+        <v>-1.00841970629835</v>
       </c>
     </row>
     <row r="468">
@@ -6143,7 +6146,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.370276302241341</v>
+        <v>-0.215824131422027</v>
       </c>
     </row>
     <row r="469">
@@ -6154,7 +6157,7 @@
         <v>16</v>
       </c>
       <c r="C469" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.596374656297365</v>
       </c>
     </row>
     <row r="470">
@@ -6187,7 +6190,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.206222525808044</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="473">
@@ -6198,7 +6201,7 @@
         <v>16</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.160537891382081</v>
+        <v>-0.199089903811225</v>
       </c>
     </row>
     <row r="474">
@@ -6209,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.191583955655771</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="475">
@@ -6231,7 +6234,7 @@
         <v>16</v>
       </c>
       <c r="C476" t="n">
-        <v>-0.244488114803235</v>
+        <v>-0.259992286355525</v>
       </c>
     </row>
     <row r="477">
@@ -6275,7 +6278,7 @@
         <v>16</v>
       </c>
       <c r="C480" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.300937472658246</v>
       </c>
     </row>
     <row r="481">
@@ -6286,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>0.202428421217281</v>
+        <v>0.389144739658774</v>
       </c>
     </row>
     <row r="482">
@@ -6297,7 +6300,7 @@
         <v>16</v>
       </c>
       <c r="C482" t="n">
-        <v>0.366225189572023</v>
+        <v>-0.68977697036919</v>
       </c>
     </row>
     <row r="483">
@@ -6308,7 +6311,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="n">
-        <v>-0.158509232822537</v>
+        <v>-0.242575511617651</v>
       </c>
     </row>
     <row r="484">
@@ -6319,7 +6322,7 @@
         <v>16</v>
       </c>
       <c r="C484" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.07487368666258</v>
       </c>
     </row>
     <row r="485">
@@ -6330,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.147959183673469</v>
+        <v>0.03184349913639</v>
       </c>
     </row>
     <row r="486">
@@ -6341,7 +6344,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.315801106246195</v>
+        <v>-0.634496990578179</v>
       </c>
     </row>
     <row r="487">
@@ -6352,7 +6355,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.514771557082622</v>
       </c>
     </row>
     <row r="488">
@@ -6374,7 +6377,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.223627278653324</v>
       </c>
     </row>
     <row r="490">
@@ -6385,7 +6388,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-1.22719500453373</v>
+        <v>-0.496434208837103</v>
       </c>
     </row>
     <row r="491">
@@ -6396,7 +6399,7 @@
         <v>16</v>
       </c>
       <c r="C491" t="n">
-        <v>0.208135610355187</v>
+        <v>-1.35911026173688</v>
       </c>
     </row>
     <row r="492">
@@ -6407,7 +6410,7 @@
         <v>16</v>
       </c>
       <c r="C492" t="n">
-        <v>-0.184634658371786</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="493">
@@ -6418,7 +6421,7 @@
         <v>16</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.227331837492184</v>
+        <v>-0.510788246354487</v>
       </c>
     </row>
     <row r="494">
@@ -6440,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-4.05365741206325</v>
+        <v>-0.471407720676853</v>
       </c>
     </row>
     <row r="496">
@@ -6473,7 +6476,7 @@
         <v>16</v>
       </c>
       <c r="C498" t="n">
-        <v>-0.161042777830515</v>
+        <v>-0.446588498775995</v>
       </c>
     </row>
     <row r="499">
@@ -6484,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.192115849668161</v>
       </c>
     </row>
     <row r="500">
@@ -6495,7 +6498,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.169275831530427</v>
+        <v>-0.259601103408333</v>
       </c>
     </row>
     <row r="501">
@@ -6506,7 +6509,7 @@
         <v>16</v>
       </c>
       <c r="C501" t="n">
-        <v>-0.147959183673469</v>
+        <v>-4.83670379110274</v>
       </c>
     </row>
     <row r="502">
@@ -6517,7 +6520,7 @@
         <v>16</v>
       </c>
       <c r="C502" t="n">
-        <v>-0.6826670846558</v>
+        <v>-0.552158906895691</v>
       </c>
     </row>
     <row r="503">
@@ -6528,7 +6531,7 @@
         <v>16</v>
       </c>
       <c r="C503" t="n">
-        <v>-1.75150672331557</v>
+        <v>-0.842396396580577</v>
       </c>
     </row>
     <row r="504">
@@ -6539,7 +6542,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.181584077645763</v>
+        <v>-0.816112240621358</v>
       </c>
     </row>
     <row r="505">
@@ -6550,7 +6553,7 @@
         <v>16</v>
       </c>
       <c r="C505" t="n">
-        <v>-0.00169085066072294</v>
+        <v>-0.268775169250796</v>
       </c>
     </row>
     <row r="506">
@@ -6561,7 +6564,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>0.0942131295075566</v>
+        <v>0.175878722747987</v>
       </c>
     </row>
     <row r="507">
@@ -6572,7 +6575,7 @@
         <v>16</v>
       </c>
       <c r="C507" t="n">
-        <v>-0.155565135102683</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="508">
@@ -6594,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.497274811890638</v>
+        <v>-2.02244709134378</v>
       </c>
     </row>
     <row r="510">
@@ -6605,7 +6608,7 @@
         <v>16</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.147959183673469</v>
+        <v>-20.530114761148</v>
       </c>
     </row>
     <row r="511">
@@ -6638,7 +6641,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.166740374656706</v>
+        <v>-0.164494898327266</v>
       </c>
     </row>
     <row r="514">
@@ -6649,7 +6652,7 @@
         <v>16</v>
       </c>
       <c r="C514" t="n">
-        <v>-1.06608820859062</v>
+        <v>-0.250119085375024</v>
       </c>
     </row>
     <row r="515">
@@ -6660,7 +6663,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.18438758992657</v>
+        <v>-0.436908486404199</v>
       </c>
     </row>
     <row r="516">
@@ -6671,7 +6674,7 @@
         <v>16</v>
       </c>
       <c r="C516" t="n">
-        <v>-0.413127489406026</v>
+        <v>-0.109022826847128</v>
       </c>
     </row>
     <row r="517">
@@ -6682,7 +6685,7 @@
         <v>16</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.557846060511992</v>
+        <v>-0.503788790120088</v>
       </c>
     </row>
     <row r="518">
@@ -6693,7 +6696,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.163899819179939</v>
+        <v>-0.15539456378776</v>
       </c>
     </row>
     <row r="519">
@@ -6704,7 +6707,7 @@
         <v>16</v>
       </c>
       <c r="C519" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.312375055055682</v>
       </c>
     </row>
     <row r="520">
@@ -6715,7 +6718,7 @@
         <v>16</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.267604300564585</v>
       </c>
     </row>
     <row r="521">
@@ -6726,7 +6729,7 @@
         <v>16</v>
       </c>
       <c r="C521" t="n">
-        <v>-1.35843506459282</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="522">
@@ -6737,7 +6740,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.537421007348805</v>
+        <v>-0.204105970238782</v>
       </c>
     </row>
     <row r="523">
@@ -6759,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.226945097595405</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="525">
@@ -6770,7 +6773,7 @@
         <v>16</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.181084329739427</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="526">
@@ -6781,7 +6784,7 @@
         <v>16</v>
       </c>
       <c r="C526" t="n">
-        <v>-0.155644856889547</v>
+        <v>-27.1584598498204</v>
       </c>
     </row>
     <row r="527">
@@ -6792,7 +6795,7 @@
         <v>16</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.193380472081775</v>
+        <v>-0.154729688926968</v>
       </c>
     </row>
     <row r="528">
@@ -6803,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.01809396266882</v>
       </c>
     </row>
     <row r="529">
@@ -6814,7 +6817,7 @@
         <v>16</v>
       </c>
       <c r="C529" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.22182525829976</v>
       </c>
     </row>
     <row r="530">
@@ -6825,7 +6828,7 @@
         <v>16</v>
       </c>
       <c r="C530" t="n">
-        <v>-0.662028954123404</v>
+        <v>-0.681628389835696</v>
       </c>
     </row>
     <row r="531">
@@ -6836,7 +6839,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.01174544597459</v>
       </c>
     </row>
     <row r="532">
@@ -6847,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.18635287096159</v>
+        <v>-0.268635594098124</v>
       </c>
     </row>
     <row r="533">
@@ -6858,7 +6861,7 @@
         <v>16</v>
       </c>
       <c r="C533" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.401986639159999</v>
       </c>
     </row>
     <row r="534">
@@ -6869,7 +6872,7 @@
         <v>16</v>
       </c>
       <c r="C534" t="n">
-        <v>-0.147959183673469</v>
+        <v>0.419548861126578</v>
       </c>
     </row>
     <row r="535">
@@ -6880,7 +6883,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.202143903707766</v>
+        <v>-0.551871297639033</v>
       </c>
     </row>
     <row r="536">
@@ -6913,7 +6916,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.205902851909028</v>
+        <v>-0.204752241448349</v>
       </c>
     </row>
     <row r="539">
@@ -6935,7 +6938,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.876509001499754</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="541">
@@ -6946,7 +6949,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.501066617379183</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="542">
@@ -6957,7 +6960,7 @@
         <v>16</v>
       </c>
       <c r="C542" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.207690378143265</v>
       </c>
     </row>
     <row r="543">
@@ -6968,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.276973984313993</v>
+        <v>-1.02351322572408</v>
       </c>
     </row>
     <row r="544">
@@ -6979,7 +6982,7 @@
         <v>16</v>
       </c>
       <c r="C544" t="n">
-        <v>-0.164604147413448</v>
+        <v>-8.01297519835059</v>
       </c>
     </row>
     <row r="545">
@@ -6990,7 +6993,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>0.314087820535284</v>
+        <v>0.430681714145438</v>
       </c>
     </row>
     <row r="546">
@@ -7001,7 +7004,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.288850795686463</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="547">
@@ -7012,7 +7015,7 @@
         <v>16</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.390653507351844</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="548">
@@ -7023,7 +7026,7 @@
         <v>16</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.319739641204106</v>
+        <v>-0.321043069398222</v>
       </c>
     </row>
     <row r="549">
@@ -7034,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.146512220058657</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="550">
@@ -7056,7 +7059,7 @@
         <v>16</v>
       </c>
       <c r="C551" t="n">
-        <v>-0.503354044679814</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="552">
@@ -7067,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.353304179995756</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="553">
@@ -7078,7 +7081,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.85370933069007</v>
       </c>
     </row>
     <row r="554">
@@ -7089,7 +7092,7 @@
         <v>16</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.56532447720231</v>
       </c>
     </row>
     <row r="555">
@@ -7100,7 +7103,7 @@
         <v>16</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.278691137675487</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="556">
@@ -7111,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.670541582892225</v>
+        <v>-0.330461129284946</v>
       </c>
     </row>
     <row r="557">
@@ -7122,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>0.362514523498701</v>
+        <v>-0.358188106627344</v>
       </c>
     </row>
     <row r="558">
@@ -7144,7 +7147,7 @@
         <v>16</v>
       </c>
       <c r="C559" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.78765803673197</v>
       </c>
     </row>
     <row r="560">
@@ -7155,7 +7158,7 @@
         <v>16</v>
       </c>
       <c r="C560" t="n">
-        <v>-0.284947217720333</v>
+        <v>-0.813742147872818</v>
       </c>
     </row>
     <row r="561">
@@ -7166,7 +7169,7 @@
         <v>16</v>
       </c>
       <c r="C561" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.257117818716658</v>
       </c>
     </row>
     <row r="562">
@@ -7177,7 +7180,7 @@
         <v>16</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.451974941326972</v>
+        <v>-0.271508275316337</v>
       </c>
     </row>
     <row r="563">
@@ -7188,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.341614783602238</v>
+        <v>-0.640554762430117</v>
       </c>
     </row>
     <row r="564">
@@ -7210,7 +7213,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.915686656373213</v>
+        <v>-0.255762033490962</v>
       </c>
     </row>
     <row r="566">
@@ -7243,7 +7246,7 @@
         <v>16</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.260674757236829</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="569">
@@ -7254,7 +7257,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.45211147674894</v>
+        <v>-0.594948852665327</v>
       </c>
     </row>
     <row r="570">
@@ -7265,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.920325115742381</v>
       </c>
     </row>
     <row r="571">
@@ -7276,7 +7279,7 @@
         <v>16</v>
       </c>
       <c r="C571" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.274060164064166</v>
       </c>
     </row>
     <row r="572">
@@ -7298,7 +7301,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.230983179262053</v>
+        <v>-0.357074386984745</v>
       </c>
     </row>
     <row r="574">
@@ -7309,7 +7312,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.147959183673469</v>
+        <v>0.460539479373549</v>
       </c>
     </row>
     <row r="575">
@@ -7331,7 +7334,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-9.11198370392899</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="577">
@@ -7342,7 +7345,7 @@
         <v>16</v>
       </c>
       <c r="C577" t="n">
-        <v>-0.222565446494176</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="578">
@@ -7364,7 +7367,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.147959183673469</v>
+        <v>-23.4782001251586</v>
       </c>
     </row>
     <row r="580">
@@ -7375,7 +7378,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-2.3078099585962</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="581">
@@ -7397,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.163740670629511</v>
+        <v>-0.179288591648217</v>
       </c>
     </row>
     <row r="583">
@@ -7408,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.12942119966113</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="584">
@@ -7430,7 +7433,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.119739976209475</v>
       </c>
     </row>
     <row r="586">
@@ -7441,7 +7444,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.120879286000974</v>
       </c>
     </row>
     <row r="587">
@@ -7452,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.408226939767982</v>
+        <v>0.0551725485657261</v>
       </c>
     </row>
     <row r="588">
@@ -7463,7 +7466,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.237277576395505</v>
+        <v>-0.132574976221047</v>
       </c>
     </row>
     <row r="589">
@@ -7474,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>0.307647028253185</v>
+        <v>-0.186258363696784</v>
       </c>
     </row>
     <row r="590">
@@ -7485,7 +7488,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.381199080732888</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="591">
@@ -7496,7 +7499,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.288929743367697</v>
+        <v>-0.577358026253588</v>
       </c>
     </row>
     <row r="592">
@@ -7507,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.341934262995305</v>
+        <v>-0.881214250348339</v>
       </c>
     </row>
     <row r="593">
@@ -7518,7 +7521,7 @@
         <v>16</v>
       </c>
       <c r="C593" t="n">
-        <v>-0.277389947735498</v>
+        <v>-0.305192504576172</v>
       </c>
     </row>
     <row r="594">
@@ -7529,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.364905400021516</v>
+        <v>-0.356702679628597</v>
       </c>
     </row>
     <row r="595">
@@ -7540,7 +7543,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>0.424055716159494</v>
+        <v>0.352003538779878</v>
       </c>
     </row>
     <row r="596">
@@ -7551,7 +7554,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.185513889611908</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="597">
@@ -7584,7 +7587,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.205416436642604</v>
+        <v>-0.170021026291264</v>
       </c>
     </row>
     <row r="600">
@@ -7595,7 +7598,7 @@
         <v>16</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.637525378578605</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="601">
@@ -7617,7 +7620,7 @@
         <v>16</v>
       </c>
       <c r="C602" t="n">
-        <v>-0.0143155399156989</v>
+        <v>-0.319182672440431</v>
       </c>
     </row>
     <row r="603">
@@ -7639,7 +7642,7 @@
         <v>16</v>
       </c>
       <c r="C604" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.114573657823117</v>
       </c>
     </row>
     <row r="605">
@@ -7661,7 +7664,7 @@
         <v>16</v>
       </c>
       <c r="C606" t="n">
-        <v>-3.05198314757885</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="607">
@@ -7672,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.202934770600527</v>
+        <v>-0.276034195603216</v>
       </c>
     </row>
     <row r="608">
@@ -7683,7 +7686,7 @@
         <v>16</v>
       </c>
       <c r="C608" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.27173764806208</v>
       </c>
     </row>
     <row r="609">
@@ -7694,7 +7697,7 @@
         <v>16</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.595571577870776</v>
+        <v>-0.136862407574702</v>
       </c>
     </row>
     <row r="610">
@@ -7705,7 +7708,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.330160773977927</v>
       </c>
     </row>
     <row r="611">
@@ -7716,7 +7719,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.174365260760325</v>
+        <v>-0.282777123258629</v>
       </c>
     </row>
     <row r="612">
@@ -7727,7 +7730,7 @@
         <v>16</v>
       </c>
       <c r="C612" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.30960125403375</v>
       </c>
     </row>
     <row r="613">
@@ -7738,7 +7741,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.162955799906863</v>
+        <v>-0.273127256927671</v>
       </c>
     </row>
     <row r="614">
@@ -7749,7 +7752,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.33070985926378</v>
+        <v>-0.232343332846618</v>
       </c>
     </row>
     <row r="615">
@@ -7760,7 +7763,7 @@
         <v>16</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.314204172858861</v>
+        <v>-0.0180615476662911</v>
       </c>
     </row>
     <row r="616">
@@ -7771,7 +7774,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>-1.19060597685579</v>
+        <v>-0.176243965567192</v>
       </c>
     </row>
     <row r="617">
@@ -7782,7 +7785,7 @@
         <v>16</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.147959183673469</v>
+        <v>-13.6501379725448</v>
       </c>
     </row>
     <row r="618">
@@ -7804,7 +7807,7 @@
         <v>16</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.370905717137754</v>
+        <v>-0.203046871423873</v>
       </c>
     </row>
     <row r="620">
@@ -7815,7 +7818,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.161973230760357</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="621">
@@ -7859,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.542462809111527</v>
+        <v>-0.540914149881538</v>
       </c>
     </row>
     <row r="625">
@@ -7881,7 +7884,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.611359228713963</v>
+        <v>-1.98683683954983</v>
       </c>
     </row>
     <row r="627">
@@ -7892,7 +7895,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.76516134004042</v>
+        <v>-0.566728591692263</v>
       </c>
     </row>
     <row r="628">
@@ -7903,7 +7906,7 @@
         <v>16</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.441276933866664</v>
+        <v>-0.600087683169726</v>
       </c>
     </row>
     <row r="629">
@@ -7914,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.542627944568734</v>
       </c>
     </row>
     <row r="630">
@@ -7947,7 +7950,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.274583891901648</v>
+        <v>-0.693939925025364</v>
       </c>
     </row>
     <row r="633">
@@ -7969,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.292823965926881</v>
+        <v>-0.226525106970014</v>
       </c>
     </row>
     <row r="635">
@@ -7991,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.617185302046949</v>
+        <v>-0.165432390555848</v>
       </c>
     </row>
     <row r="637">
@@ -8002,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.356670750970722</v>
+        <v>-0.415648498218058</v>
       </c>
     </row>
     <row r="638">
@@ -8013,7 +8016,7 @@
         <v>16</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.573053566680105</v>
+        <v>-0.137303004553547</v>
       </c>
     </row>
     <row r="639">
@@ -8035,7 +8038,7 @@
         <v>16</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.341959564585296</v>
+        <v>-1.2886750456934</v>
       </c>
     </row>
     <row r="641">
@@ -8046,7 +8049,7 @@
         <v>16</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.463242193495799</v>
+        <v>-0.373453147076918</v>
       </c>
     </row>
     <row r="642">
@@ -8057,7 +8060,7 @@
         <v>16</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.960148138691914</v>
       </c>
     </row>
     <row r="643">
@@ -8079,7 +8082,7 @@
         <v>16</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.147959183673469</v>
+        <v>0.410185597935947</v>
       </c>
     </row>
     <row r="645">
@@ -8090,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.357004319714118</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="646">
@@ -8101,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.509893755767374</v>
       </c>
     </row>
     <row r="647">
@@ -8112,7 +8115,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.16162508793075</v>
       </c>
     </row>
     <row r="648">
@@ -8123,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.423082963116489</v>
+        <v>-3.84890778972348</v>
       </c>
     </row>
     <row r="649">
@@ -8134,7 +8137,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>-0.433483876994315</v>
+        <v>-0.0774596031242365</v>
       </c>
     </row>
     <row r="650">
@@ -8178,7 +8181,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.334660404207053</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="654">
@@ -8211,7 +8214,7 @@
         <v>16</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.544483045299991</v>
+        <v>-0.479672631138811</v>
       </c>
     </row>
     <row r="657">
@@ -8222,7 +8225,7 @@
         <v>16</v>
       </c>
       <c r="C657" t="n">
-        <v>-0.147959183673469</v>
+        <v>-8.25714855505231</v>
       </c>
     </row>
     <row r="658">
@@ -8244,7 +8247,7 @@
         <v>16</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.158237419060025</v>
+        <v>-0.279726397299001</v>
       </c>
     </row>
     <row r="660">
@@ -8266,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.23251196221974</v>
+        <v>-1.33392801375705</v>
       </c>
     </row>
     <row r="662">
@@ -8277,7 +8280,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.244733779666756</v>
+        <v>-0.469880845305177</v>
       </c>
     </row>
     <row r="663">
@@ -8288,7 +8291,7 @@
         <v>16</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.664303060940629</v>
+        <v>-0.532696785597442</v>
       </c>
     </row>
     <row r="664">
@@ -8310,7 +8313,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.264642700071674</v>
       </c>
     </row>
     <row r="666">
@@ -8321,7 +8324,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.2316053195702</v>
       </c>
     </row>
     <row r="667">
@@ -8332,7 +8335,7 @@
         <v>16</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.581845309936073</v>
+        <v>-0.458589241120391</v>
       </c>
     </row>
     <row r="668">
@@ -8343,7 +8346,7 @@
         <v>16</v>
       </c>
       <c r="C668" t="n">
-        <v>-0.282495694240462</v>
+        <v>-1.01396366786683</v>
       </c>
     </row>
     <row r="669">
@@ -8354,7 +8357,7 @@
         <v>16</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.139620821414247</v>
       </c>
     </row>
     <row r="670">
@@ -8376,7 +8379,7 @@
         <v>16</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.370310374095727</v>
+        <v>-0.219892942960608</v>
       </c>
     </row>
     <row r="672">
@@ -8387,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.25295098154335</v>
+        <v>-0.253319211431646</v>
       </c>
     </row>
     <row r="673">
@@ -8398,7 +8401,7 @@
         <v>16</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.334437448057085</v>
+        <v>-0.278622469618366</v>
       </c>
     </row>
     <row r="674">
@@ -8409,7 +8412,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.147959183673469</v>
+        <v>-7.97575537309692</v>
       </c>
     </row>
     <row r="675">
@@ -8420,7 +8423,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.838405415921201</v>
       </c>
     </row>
     <row r="676">
@@ -8431,7 +8434,7 @@
         <v>16</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.359078712715647</v>
       </c>
     </row>
     <row r="677">
@@ -8442,7 +8445,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.312418672435588</v>
+        <v>-0.328029851130511</v>
       </c>
     </row>
     <row r="678">
@@ -8453,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.417948509578685</v>
+        <v>-2.72027538845596</v>
       </c>
     </row>
     <row r="679">
@@ -8475,7 +8478,7 @@
         <v>16</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.17026504498509</v>
+        <v>-0.391033595545623</v>
       </c>
     </row>
     <row r="681">
@@ -8486,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-1.93019554485035</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="682">
@@ -8497,7 +8500,7 @@
         <v>16</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.19201847503524</v>
       </c>
     </row>
     <row r="683">
@@ -8508,7 +8511,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.223135477563507</v>
+        <v>-0.0564470889402868</v>
       </c>
     </row>
     <row r="684">
@@ -8519,7 +8522,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.250132811627765</v>
       </c>
     </row>
     <row r="685">
@@ -8530,7 +8533,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>-1.20281114595734</v>
+        <v>-0.314012009476859</v>
       </c>
     </row>
     <row r="686">
@@ -8541,7 +8544,7 @@
         <v>16</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.238001258945248</v>
       </c>
     </row>
     <row r="687">
@@ -8552,7 +8555,7 @@
         <v>16</v>
       </c>
       <c r="C687" t="n">
-        <v>-0.15002353012208</v>
+        <v>-0.1541377064453</v>
       </c>
     </row>
     <row r="688">
@@ -8563,7 +8566,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.423832784038748</v>
+        <v>-3.57247729871024</v>
       </c>
     </row>
     <row r="689">
@@ -8574,7 +8577,7 @@
         <v>16</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.308460498150622</v>
+        <v>-1.44927776916499</v>
       </c>
     </row>
     <row r="690">
@@ -8585,7 +8588,7 @@
         <v>16</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.98361101099433</v>
+        <v>-0.366231640444097</v>
       </c>
     </row>
     <row r="691">
@@ -8596,7 +8599,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-2.26179047932293</v>
+        <v>-0.452004248013495</v>
       </c>
     </row>
     <row r="692">
@@ -8607,7 +8610,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.304227065626355</v>
+        <v>-0.549854314960809</v>
       </c>
     </row>
     <row r="693">
@@ -8618,7 +8621,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.18566161706005</v>
       </c>
     </row>
     <row r="694">
@@ -8640,7 +8643,7 @@
         <v>16</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.172294257781287</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="696">
@@ -8651,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.226223201646256</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="697">
@@ -8662,7 +8665,7 @@
         <v>16</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.71693219144763</v>
+        <v>-0.403535528375562</v>
       </c>
     </row>
     <row r="698">
@@ -8673,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.577946360216559</v>
+        <v>-0.0110032578465327</v>
       </c>
     </row>
     <row r="699">
@@ -8684,7 +8687,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.284994249339298</v>
+        <v>-0.243533355728769</v>
       </c>
     </row>
     <row r="700">
@@ -8717,7 +8720,7 @@
         <v>16</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.308734738952295</v>
+        <v>-0.231633256133459</v>
       </c>
     </row>
     <row r="703">
@@ -8728,7 +8731,7 @@
         <v>16</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.14795918367347</v>
+        <v>-5.08876941522567</v>
       </c>
     </row>
     <row r="704">
@@ -8750,7 +8753,7 @@
         <v>16</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.489951176951149</v>
+        <v>-16.708386095301</v>
       </c>
     </row>
     <row r="706">
@@ -8761,7 +8764,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-3.01989600327736</v>
+        <v>-0.230211765015368</v>
       </c>
     </row>
     <row r="707">
@@ -8772,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-1.45827726816401</v>
+        <v>-0.036369093221998</v>
       </c>
     </row>
     <row r="708">
@@ -8783,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.397364107537871</v>
+        <v>-0.14435991992456</v>
       </c>
     </row>
     <row r="709">
@@ -8794,7 +8797,7 @@
         <v>16</v>
       </c>
       <c r="C709" t="n">
-        <v>-3.36366166546699</v>
+        <v>-1.19096500282888</v>
       </c>
     </row>
     <row r="710">
@@ -8805,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.92648024081558</v>
+        <v>-0.565723914786983</v>
       </c>
     </row>
     <row r="711">
@@ -8816,7 +8819,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.131937372427475</v>
       </c>
     </row>
     <row r="712">
@@ -8827,7 +8830,7 @@
         <v>16</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.10527300512188</v>
       </c>
     </row>
     <row r="713">
@@ -8871,7 +8874,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.65855570436917</v>
+        <v>-0.44174985090691</v>
       </c>
     </row>
     <row r="717">
@@ -8893,7 +8896,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.252982985450709</v>
+        <v>-0.152672924025735</v>
       </c>
     </row>
     <row r="719">
@@ -8915,7 +8918,7 @@
         <v>16</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.225640182714884</v>
+        <v>-1.17186743515114</v>
       </c>
     </row>
     <row r="721">
@@ -8926,7 +8929,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.397333886116909</v>
+        <v>-0.87011787965713</v>
       </c>
     </row>
     <row r="722">
@@ -8937,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.24376983180102</v>
+        <v>-0.39440956900317</v>
       </c>
     </row>
     <row r="723">
@@ -8959,7 +8962,7 @@
         <v>16</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.14795918367347</v>
+        <v>-3.59132109261532</v>
       </c>
     </row>
     <row r="725">
@@ -8970,7 +8973,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.187918203474336</v>
+        <v>-0.00918138749883735</v>
       </c>
     </row>
     <row r="726">
@@ -8981,7 +8984,7 @@
         <v>16</v>
       </c>
       <c r="C726" t="n">
-        <v>-0.174281697376363</v>
+        <v>-0.197569386084182</v>
       </c>
     </row>
     <row r="727">
@@ -9003,7 +9006,7 @@
         <v>16</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.636184363521045</v>
+        <v>-0.662786542431412</v>
       </c>
     </row>
     <row r="729">
@@ -9014,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.255386760418788</v>
+        <v>-0.308050068682609</v>
       </c>
     </row>
     <row r="730">
@@ -9025,7 +9028,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>0.517327685695064</v>
+        <v>-0.0256679999256364</v>
       </c>
     </row>
     <row r="731">
@@ -9036,7 +9039,7 @@
         <v>16</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.147959183673469</v>
+        <v>-14.849226666884</v>
       </c>
     </row>
     <row r="732">
@@ -9069,7 +9072,7 @@
         <v>16</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.147959183673469</v>
+        <v>-25.7540337966949</v>
       </c>
     </row>
     <row r="735">
@@ -9080,7 +9083,7 @@
         <v>16</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.345572746868335</v>
+        <v>-0.434699391171963</v>
       </c>
     </row>
     <row r="736">
@@ -9102,7 +9105,7 @@
         <v>16</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.324647006652181</v>
       </c>
     </row>
     <row r="738">
@@ -9190,7 +9193,7 @@
         <v>16</v>
       </c>
       <c r="C745" t="n">
-        <v>0.0567314775377217</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="746">
@@ -9201,7 +9204,7 @@
         <v>16</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.495965401634143</v>
+        <v>-0.42649251104958</v>
       </c>
     </row>
     <row r="747">
@@ -9223,7 +9226,7 @@
         <v>16</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.579493795629973</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="749">
@@ -9234,7 +9237,7 @@
         <v>16</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.313973183640948</v>
+        <v>-0.325539072175728</v>
       </c>
     </row>
     <row r="750">
@@ -9245,7 +9248,7 @@
         <v>16</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.183430055650364</v>
+        <v>-0.215575177183375</v>
       </c>
     </row>
     <row r="751">
@@ -9256,7 +9259,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.715033725192934</v>
+        <v>0.728206005330639</v>
       </c>
     </row>
     <row r="752">
@@ -9267,7 +9270,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.496046581959255</v>
+        <v>-2.12454335545024</v>
       </c>
     </row>
     <row r="753">
@@ -9278,7 +9281,7 @@
         <v>16</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.183804772640431</v>
       </c>
     </row>
     <row r="754">
@@ -9289,7 +9292,7 @@
         <v>16</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.685835316178019</v>
       </c>
     </row>
     <row r="755">
@@ -9311,7 +9314,7 @@
         <v>16</v>
       </c>
       <c r="C756" t="n">
-        <v>-1.77888170524317</v>
+        <v>-0.286223767087015</v>
       </c>
     </row>
     <row r="757">
@@ -9322,7 +9325,7 @@
         <v>16</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.403056627987552</v>
+        <v>-0.622138258165586</v>
       </c>
     </row>
     <row r="758">
@@ -9333,7 +9336,7 @@
         <v>16</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.526083988759809</v>
+        <v>-0.146900912651628</v>
       </c>
     </row>
     <row r="759">
@@ -9344,7 +9347,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.272641251793502</v>
+        <v>-0.42531333332767</v>
       </c>
     </row>
     <row r="760">
@@ -9355,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.136470280891431</v>
       </c>
     </row>
     <row r="761">
@@ -9377,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.467544562807124</v>
+        <v>-0.304868937061783</v>
       </c>
     </row>
     <row r="763">
@@ -9388,7 +9391,7 @@
         <v>16</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.595877597708268</v>
+        <v>-0.0691086173412836</v>
       </c>
     </row>
     <row r="764">
@@ -9399,7 +9402,7 @@
         <v>16</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.478968583660773</v>
       </c>
     </row>
     <row r="765">
@@ -9421,7 +9424,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.382036080213432</v>
+        <v>-0.420775867488613</v>
       </c>
     </row>
     <row r="767">
@@ -9432,7 +9435,7 @@
         <v>16</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.225328846055978</v>
+        <v>-15.9780979215946</v>
       </c>
     </row>
     <row r="768">
@@ -9443,7 +9446,7 @@
         <v>16</v>
       </c>
       <c r="C768" t="n">
-        <v>0.23052459783868</v>
+        <v>-0.135200218177455</v>
       </c>
     </row>
     <row r="769">
@@ -9454,7 +9457,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-2.94840292944804</v>
+        <v>-2.33646438929172</v>
       </c>
     </row>
     <row r="770">
@@ -9476,7 +9479,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.329860878120191</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="772">
@@ -9487,7 +9490,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>0.365709306864191</v>
+        <v>-0.518598617474384</v>
       </c>
     </row>
     <row r="773">
@@ -9498,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.28007308238399</v>
+        <v>-0.219365699198388</v>
       </c>
     </row>
     <row r="774">
@@ -9531,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.586053015162725</v>
+        <v>-1.97764316262082</v>
       </c>
     </row>
     <row r="777">
@@ -9542,7 +9545,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.49711435671188</v>
       </c>
     </row>
     <row r="778">
@@ -9553,7 +9556,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.194573665228758</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="779">
@@ -9564,7 +9567,7 @@
         <v>16</v>
       </c>
       <c r="C779" t="n">
-        <v>0.206966377223649</v>
+        <v>0.0358687856799828</v>
       </c>
     </row>
     <row r="780">
@@ -9575,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.592306880531136</v>
+        <v>-0.292897650671207</v>
       </c>
     </row>
     <row r="781">
@@ -9586,7 +9589,7 @@
         <v>16</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.119174583599244</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="782">
@@ -9619,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.190699442496449</v>
+        <v>-0.220978398834593</v>
       </c>
     </row>
     <row r="785">
@@ -9630,7 +9633,7 @@
         <v>16</v>
       </c>
       <c r="C785" t="n">
-        <v>-0.358584640488617</v>
+        <v>-0.46333785355032</v>
       </c>
     </row>
     <row r="786">
@@ -9641,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.137150396568866</v>
+        <v>-0.0853024823757873</v>
       </c>
     </row>
     <row r="787">
@@ -9652,7 +9655,7 @@
         <v>16</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.389454640423055</v>
+        <v>-0.480040625039517</v>
       </c>
     </row>
     <row r="788">
@@ -9663,7 +9666,7 @@
         <v>16</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.564019619803117</v>
+        <v>-0.246997934144768</v>
       </c>
     </row>
     <row r="789">
@@ -9674,7 +9677,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.554688546878582</v>
+        <v>-0.201120585985387</v>
       </c>
     </row>
     <row r="790">
@@ -9685,7 +9688,7 @@
         <v>16</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.219957390130365</v>
+        <v>-0.230189688142747</v>
       </c>
     </row>
     <row r="791">
@@ -9707,7 +9710,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.193250431358257</v>
+        <v>-0.174490106512049</v>
       </c>
     </row>
     <row r="793">
@@ -9718,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.756210814107358</v>
+        <v>-0.896604541172228</v>
       </c>
     </row>
     <row r="794">
@@ -9729,7 +9732,7 @@
         <v>16</v>
       </c>
       <c r="C794" t="n">
-        <v>-1.07769351430948</v>
+        <v>-0.799637495441831</v>
       </c>
     </row>
     <row r="795">
@@ -9740,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-1.08268815478619</v>
+        <v>-1.29758566077748</v>
       </c>
     </row>
     <row r="796">
@@ -9751,7 +9754,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.724546880627837</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="797">
@@ -9762,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.715938463324582</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="798">
@@ -9773,7 +9776,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.902607632866127</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="799">
@@ -9806,7 +9809,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.148624011011324</v>
+        <v>-0.0691998512616885</v>
       </c>
     </row>
     <row r="802">
@@ -9817,7 +9820,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.195763462854086</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="803">
@@ -9828,7 +9831,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.225172102386529</v>
+        <v>-0.212715219242411</v>
       </c>
     </row>
     <row r="804">
@@ -9839,7 +9842,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.971997885563385</v>
+        <v>-0.590917942764837</v>
       </c>
     </row>
     <row r="805">
@@ -9872,7 +9875,7 @@
         <v>16</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.550822481692416</v>
       </c>
     </row>
     <row r="808">
@@ -9883,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>0.22122475337432</v>
+        <v>0.205398658187119</v>
       </c>
     </row>
     <row r="809">
@@ -9894,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.265412961937116</v>
       </c>
     </row>
     <row r="810">
@@ -9916,7 +9919,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.233802602225864</v>
+        <v>-0.625087301742838</v>
       </c>
     </row>
     <row r="812">
@@ -9927,7 +9930,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.332197443066032</v>
+        <v>0.121817105628389</v>
       </c>
     </row>
     <row r="813">
@@ -9949,7 +9952,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.954446293885177</v>
       </c>
     </row>
     <row r="815">
@@ -9960,7 +9963,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.147959183673469</v>
+        <v>-4.97582411950337</v>
       </c>
     </row>
     <row r="816">
@@ -9971,7 +9974,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.183212785224771</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="817">
@@ -9993,7 +9996,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.147959183673469</v>
+        <v>0.748887565917588</v>
       </c>
     </row>
     <row r="819">
@@ -10004,7 +10007,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>0.285595218821619</v>
+        <v>0.0406341783787493</v>
       </c>
     </row>
     <row r="820">
@@ -10015,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>0.257354947695709</v>
+        <v>0.271505913224866</v>
       </c>
     </row>
     <row r="821">
@@ -10026,7 +10029,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.45788805589727</v>
+        <v>-0.652252294945085</v>
       </c>
     </row>
     <row r="822">
@@ -10037,7 +10040,7 @@
         <v>16</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.17534507164627</v>
+        <v>-0.183061276575583</v>
       </c>
     </row>
     <row r="823">
@@ -10059,7 +10062,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.887223360675247</v>
       </c>
     </row>
     <row r="825">
@@ -10081,7 +10084,7 @@
         <v>16</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.190191265011924</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="827">
@@ -10103,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.51484910825299</v>
+        <v>-0.157905065703574</v>
       </c>
     </row>
     <row r="829">
@@ -10114,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.282802536931477</v>
+        <v>-0.292924302046992</v>
       </c>
     </row>
     <row r="830">
@@ -10125,7 +10128,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.189928178794546</v>
+        <v>-0.724410294223456</v>
       </c>
     </row>
     <row r="831">
@@ -10136,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.270427581836774</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="832">
@@ -10147,7 +10150,7 @@
         <v>16</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.967884395051868</v>
+        <v>-3.69777609064086</v>
       </c>
     </row>
     <row r="833">
@@ -10158,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.375906121530048</v>
+        <v>-1.61685532645748</v>
       </c>
     </row>
     <row r="834">
@@ -10180,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.168736978176864</v>
+        <v>-0.47700758206487</v>
       </c>
     </row>
     <row r="836">
@@ -10191,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.437399317317084</v>
+        <v>-0.137117055929322</v>
       </c>
     </row>
     <row r="837">
@@ -10202,7 +10205,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.590067824737371</v>
+        <v>-0.188371684793252</v>
       </c>
     </row>
     <row r="838">
@@ -10213,7 +10216,7 @@
         <v>16</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.232480184089015</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="839">
@@ -10224,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-1.92432972666329</v>
+        <v>-0.181913205084552</v>
       </c>
     </row>
     <row r="840">
@@ -10268,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.0826014165259255</v>
+        <v>-0.174762977189036</v>
       </c>
     </row>
     <row r="844">
@@ -10279,7 +10282,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.761530673526236</v>
+        <v>-0.571959333324331</v>
       </c>
     </row>
     <row r="845">
@@ -10290,7 +10293,7 @@
         <v>16</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.561933993044207</v>
       </c>
     </row>
     <row r="846">
@@ -10301,7 +10304,7 @@
         <v>16</v>
       </c>
       <c r="C846" t="n">
-        <v>0.174012563345444</v>
+        <v>-0.46843907700663</v>
       </c>
     </row>
     <row r="847">
@@ -10312,7 +10315,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.660347546786761</v>
+        <v>-0.442938159165689</v>
       </c>
     </row>
     <row r="848">
@@ -10323,7 +10326,7 @@
         <v>16</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.195972032787624</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="849">
@@ -10334,7 +10337,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.11988530329539</v>
       </c>
     </row>
     <row r="850">
@@ -10356,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>0.102289765123475</v>
+        <v>0.215166419479026</v>
       </c>
     </row>
     <row r="852">
@@ -10367,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.423381512116883</v>
+        <v>-0.418974236178267</v>
       </c>
     </row>
     <row r="853">
@@ -10389,7 +10392,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.83929834612268</v>
+        <v>-1.50046247183883</v>
       </c>
     </row>
     <row r="855">
@@ -10400,7 +10403,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.58513844582215</v>
+        <v>-0.197035130953359</v>
       </c>
     </row>
     <row r="856">
@@ -10411,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-1.54164424371183</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="857">
@@ -10422,7 +10425,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.309601938079974</v>
+        <v>-0.396628198009082</v>
       </c>
     </row>
     <row r="858">
@@ -10444,7 +10447,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.202288649339539</v>
+        <v>-0.189283125952434</v>
       </c>
     </row>
     <row r="860">
@@ -10455,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.178052237797402</v>
+        <v>-0.180705044793281</v>
       </c>
     </row>
     <row r="861">
@@ -10466,7 +10469,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.22701026021224</v>
       </c>
     </row>
     <row r="862">
@@ -10477,7 +10480,7 @@
         <v>16</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.363906450885701</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="863">
@@ -10488,7 +10491,7 @@
         <v>16</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.671889663071142</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="864">
@@ -10499,7 +10502,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.14795918367347</v>
+        <v>-3.48762550331347</v>
       </c>
     </row>
     <row r="865">
@@ -10510,7 +10513,7 @@
         <v>16</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.730222526651823</v>
       </c>
     </row>
     <row r="866">
@@ -10532,7 +10535,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>0.435831090035533</v>
+        <v>-0.340897111316087</v>
       </c>
     </row>
     <row r="868">
@@ -10543,7 +10546,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.443282483143074</v>
+        <v>0.495336359811553</v>
       </c>
     </row>
     <row r="869">
@@ -10554,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-1.46683641071452</v>
+        <v>-0.198671827651992</v>
       </c>
     </row>
     <row r="870">
@@ -10565,7 +10568,7 @@
         <v>16</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.451301832972621</v>
       </c>
     </row>
     <row r="871">
@@ -10587,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.545486913509417</v>
       </c>
     </row>
     <row r="873">
@@ -10620,7 +10623,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.0883224900975632</v>
+        <v>-1.0468049652012</v>
       </c>
     </row>
     <row r="876">
@@ -10631,7 +10634,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.396003012309115</v>
+        <v>-0.222168092122849</v>
       </c>
     </row>
     <row r="877">
@@ -10642,7 +10645,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.175904389861615</v>
+        <v>-0.213587387329065</v>
       </c>
     </row>
     <row r="878">
@@ -10653,7 +10656,7 @@
         <v>16</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.857289854737059</v>
       </c>
     </row>
     <row r="879">
@@ -10664,7 +10667,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>-1.59273321478843</v>
+        <v>-0.15755627160267</v>
       </c>
     </row>
     <row r="880">
@@ -10675,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.182633963029906</v>
+        <v>-0.246148334036961</v>
       </c>
     </row>
     <row r="881">
@@ -10686,7 +10689,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.260834253457516</v>
+        <v>-0.477509904588442</v>
       </c>
     </row>
     <row r="882">
@@ -10697,7 +10700,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.32511641017073</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="883">
@@ -10719,7 +10722,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.263022300014368</v>
+        <v>-32.4845961561781</v>
       </c>
     </row>
     <row r="885">
@@ -10730,7 +10733,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.411958307203362</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="886">
@@ -10741,7 +10744,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.580133863967913</v>
+        <v>-0.160798925501955</v>
       </c>
     </row>
     <row r="887">
@@ -10752,7 +10755,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.197537376132027</v>
       </c>
     </row>
     <row r="888">
@@ -10763,7 +10766,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.259129891992589</v>
+        <v>-0.396682892296035</v>
       </c>
     </row>
     <row r="889">
@@ -10774,7 +10777,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.982004187059893</v>
       </c>
     </row>
     <row r="890">
@@ -10796,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.302581830466816</v>
+        <v>-0.446486938959558</v>
       </c>
     </row>
     <row r="892">
@@ -10807,7 +10810,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.165649940621011</v>
+        <v>-0.535956918491409</v>
       </c>
     </row>
     <row r="893">
@@ -10818,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.153765824065992</v>
+        <v>-0.392686509270377</v>
       </c>
     </row>
     <row r="894">
@@ -10829,7 +10832,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.166836969771847</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="895">
@@ -10840,7 +10843,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.313539912662887</v>
+        <v>-0.679572734606443</v>
       </c>
     </row>
     <row r="896">
@@ -10851,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.363001899428688</v>
       </c>
     </row>
     <row r="897">
@@ -10873,7 +10876,7 @@
         <v>16</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.168404323585474</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="899">
@@ -10884,7 +10887,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.376589807394047</v>
+        <v>-0.512552488383882</v>
       </c>
     </row>
     <row r="900">
@@ -10895,7 +10898,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.161783109411888</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="901">
@@ -10906,7 +10909,7 @@
         <v>16</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.837035951458202</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="902">
@@ -10917,7 +10920,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.430948765142215</v>
+        <v>-1.56268146348971</v>
       </c>
     </row>
     <row r="903">
@@ -10928,7 +10931,7 @@
         <v>16</v>
       </c>
       <c r="C903" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.698269798997912</v>
       </c>
     </row>
     <row r="904">
@@ -10939,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.153435268541434</v>
+        <v>0.055362196034869</v>
       </c>
     </row>
     <row r="905">
@@ -10961,7 +10964,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.352277185043267</v>
+        <v>-0.269742311619619</v>
       </c>
     </row>
     <row r="907">
@@ -10983,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.1606749036401</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="909">
@@ -10994,7 +10997,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.532788128104094</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="910">
@@ -11005,7 +11008,7 @@
         <v>16</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.551517890910563</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="911">
@@ -11016,7 +11019,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.230312379413104</v>
+        <v>-0.235471391176634</v>
       </c>
     </row>
     <row r="912">
@@ -11027,7 +11030,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.334807783381359</v>
+        <v>-1.13704189060281</v>
       </c>
     </row>
     <row r="913">
@@ -11038,7 +11041,7 @@
         <v>16</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.509378756687233</v>
       </c>
     </row>
     <row r="914">
@@ -11049,7 +11052,7 @@
         <v>16</v>
       </c>
       <c r="C914" t="n">
-        <v>-1.11499027210248</v>
+        <v>-0.941505380826399</v>
       </c>
     </row>
     <row r="915">
@@ -11071,7 +11074,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.930984354744354</v>
+        <v>-1.84539680595023</v>
       </c>
     </row>
     <row r="917">
@@ -11082,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-2.31316314450511</v>
+        <v>-0.173395817129429</v>
       </c>
     </row>
     <row r="918">
@@ -11093,7 +11096,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.771598789571793</v>
+        <v>-0.888399733381515</v>
       </c>
     </row>
     <row r="919">
@@ -11104,7 +11107,7 @@
         <v>16</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.147959183673469</v>
+        <v>-10.8802294978872</v>
       </c>
     </row>
     <row r="920">
@@ -11115,7 +11118,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.147959183673469</v>
+        <v>-25.2997165733829</v>
       </c>
     </row>
     <row r="921">
@@ -11137,7 +11140,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.505527988309531</v>
+        <v>-0.422096343220308</v>
       </c>
     </row>
     <row r="923">
@@ -11148,7 +11151,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.27864355993258</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="924">
@@ -11192,7 +11195,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>0.0900042539511845</v>
+        <v>-0.0612474977244792</v>
       </c>
     </row>
     <row r="928">
@@ -11203,7 +11206,7 @@
         <v>16</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.3281059946705</v>
+        <v>-7.50181214953528</v>
       </c>
     </row>
     <row r="929">
@@ -11225,7 +11228,7 @@
         <v>16</v>
       </c>
       <c r="C930" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.15615104962557</v>
       </c>
     </row>
     <row r="931">
@@ -11236,7 +11239,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>0.26959260927555</v>
+        <v>-0.154048519127526</v>
       </c>
     </row>
     <row r="932">
@@ -11258,7 +11261,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.110564795643122</v>
+        <v>0.0978458552230873</v>
       </c>
     </row>
     <row r="934">
@@ -11269,7 +11272,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.273552232245659</v>
+        <v>-0.354565853578474</v>
       </c>
     </row>
     <row r="935">
@@ -11280,7 +11283,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.164498593057347</v>
+        <v>-0.184217735202815</v>
       </c>
     </row>
     <row r="936">
@@ -11291,7 +11294,7 @@
         <v>16</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.099293408875502</v>
+        <v>-0.0535993253378668</v>
       </c>
     </row>
     <row r="937">
@@ -11302,7 +11305,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.186033587918497</v>
+        <v>-0.516557762317966</v>
       </c>
     </row>
     <row r="938">
@@ -11313,7 +11316,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>0.0178664577163171</v>
+        <v>-1.56074169541902</v>
       </c>
     </row>
     <row r="939">
@@ -11335,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-2.36501703902587</v>
+        <v>-1.86160525611575</v>
       </c>
     </row>
     <row r="941">
@@ -11346,7 +11349,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.191551569243259</v>
+        <v>-0.0799734551732645</v>
       </c>
     </row>
     <row r="942">
@@ -11357,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.172568790834563</v>
+        <v>-0.21354848935921</v>
       </c>
     </row>
     <row r="943">
@@ -11368,7 +11371,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.764836943764996</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="944">
@@ -11379,7 +11382,7 @@
         <v>16</v>
       </c>
       <c r="C944" t="n">
-        <v>-1.58345238852388</v>
+        <v>-0.708415060255242</v>
       </c>
     </row>
     <row r="945">
@@ -11390,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-1.68432223817035</v>
+        <v>-0.297676691855607</v>
       </c>
     </row>
     <row r="946">
@@ -11412,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.225794029690846</v>
       </c>
     </row>
     <row r="948">
@@ -11423,7 +11426,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.308744811694655</v>
+        <v>-0.638782069435575</v>
       </c>
     </row>
     <row r="949">
@@ -11434,7 +11437,7 @@
         <v>16</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.162072626549334</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="950">
@@ -11456,7 +11459,7 @@
         <v>16</v>
       </c>
       <c r="C951" t="n">
-        <v>-0.147614338890659</v>
+        <v>-0.153318179213604</v>
       </c>
     </row>
     <row r="952">
@@ -11467,7 +11470,7 @@
         <v>16</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.224360863353766</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="953">
@@ -11478,7 +11481,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.392825066737368</v>
+        <v>-0.199060412640966</v>
       </c>
     </row>
     <row r="954">
@@ -11500,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.483573548615074</v>
+        <v>-0.349176477559145</v>
       </c>
     </row>
     <row r="956">
@@ -11511,7 +11514,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.233340827536318</v>
+        <v>-0.234485699154968</v>
       </c>
     </row>
     <row r="957">
@@ -11522,7 +11525,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.0843051240900221</v>
       </c>
     </row>
     <row r="958">
@@ -11533,7 +11536,7 @@
         <v>16</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.472073431979871</v>
+        <v>-0.331981746066142</v>
       </c>
     </row>
     <row r="959">
@@ -11544,7 +11547,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.306608439107434</v>
+        <v>0.268560419886685</v>
       </c>
     </row>
     <row r="960">
@@ -11555,7 +11558,7 @@
         <v>16</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.633782240530586</v>
+        <v>-0.312923455210357</v>
       </c>
     </row>
     <row r="961">
@@ -11577,7 +11580,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.549235103185863</v>
+        <v>-0.542744999999789</v>
       </c>
     </row>
     <row r="963">
@@ -11599,7 +11602,7 @@
         <v>16</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.153388220921634</v>
       </c>
     </row>
     <row r="965">
@@ -11610,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.472321181068991</v>
+        <v>-0.194153919264691</v>
       </c>
     </row>
     <row r="966">
@@ -11632,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.137447413486893</v>
+        <v>-0.161379028725682</v>
       </c>
     </row>
     <row r="968">
@@ -11665,7 +11668,7 @@
         <v>16</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.198029353787942</v>
       </c>
     </row>
     <row r="971">
@@ -11676,7 +11679,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.167348571298582</v>
+        <v>-0.21021948785329</v>
       </c>
     </row>
     <row r="972">
@@ -11687,7 +11690,7 @@
         <v>16</v>
       </c>
       <c r="C972" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.225421034262947</v>
       </c>
     </row>
     <row r="973">
@@ -11698,7 +11701,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-1.39171631476391</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="974">
@@ -11709,7 +11712,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.233299699441368</v>
+        <v>-0.838542832918557</v>
       </c>
     </row>
     <row r="975">
@@ -11720,7 +11723,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.615475497949278</v>
       </c>
     </row>
     <row r="976">
@@ -11742,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.346426192069797</v>
+        <v>-0.425604399981208</v>
       </c>
     </row>
     <row r="978">
@@ -11753,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.918918115064617</v>
+        <v>-0.444067088710291</v>
       </c>
     </row>
     <row r="979">
@@ -11764,7 +11767,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-1.42740629666716</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="980">
@@ -11775,7 +11778,7 @@
         <v>16</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.163754257704609</v>
+        <v>-0.154560316617006</v>
       </c>
     </row>
     <row r="981">
@@ -11786,7 +11789,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.589743761517581</v>
+        <v>0.356834061190211</v>
       </c>
     </row>
     <row r="982">
@@ -11808,7 +11811,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.231428541664463</v>
+        <v>-0.228786539817082</v>
       </c>
     </row>
     <row r="984">
@@ -11819,7 +11822,7 @@
         <v>16</v>
       </c>
       <c r="C984" t="n">
-        <v>-0.147753130575997</v>
+        <v>-0.244403804359198</v>
       </c>
     </row>
     <row r="985">
@@ -11830,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.00561539845267278</v>
+        <v>-0.393207836831694</v>
       </c>
     </row>
     <row r="986">
@@ -11841,7 +11844,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>-0.72135654291122</v>
+        <v>-0.400341232714515</v>
       </c>
     </row>
     <row r="987">
@@ -11852,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.10238551425987</v>
       </c>
     </row>
     <row r="988">
@@ -11863,7 +11866,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.206415771587409</v>
+        <v>-0.913059588300067</v>
       </c>
     </row>
     <row r="989">
@@ -11874,7 +11877,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.200711404724853</v>
+        <v>-0.972551962058624</v>
       </c>
     </row>
     <row r="990">
@@ -11885,7 +11888,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.384983018813986</v>
+        <v>0.00993042076131623</v>
       </c>
     </row>
     <row r="991">
@@ -11896,7 +11899,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.951848549294309</v>
+        <v>-0.684659643901703</v>
       </c>
     </row>
     <row r="992">
@@ -11907,7 +11910,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-3.48093743559689</v>
+        <v>-1.14222908197571</v>
       </c>
     </row>
     <row r="993">
@@ -11918,7 +11921,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.293910695319533</v>
+        <v>-0.971446462184034</v>
       </c>
     </row>
     <row r="994">
@@ -11940,7 +11943,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.149071873800705</v>
       </c>
     </row>
     <row r="996">
@@ -11951,7 +11954,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.152108409081936</v>
+        <v>-0.0746272587462655</v>
       </c>
     </row>
     <row r="997">
@@ -11962,7 +11965,7 @@
         <v>16</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.372223904114857</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="998">
@@ -11973,7 +11976,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.75609770105191</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="999">
@@ -11984,7 +11987,7 @@
         <v>16</v>
       </c>
       <c r="C999" t="n">
-        <v>-0.513189709650795</v>
+        <v>-0.581291292836939</v>
       </c>
     </row>
     <row r="1000">
@@ -12017,7 +12020,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.315064965648759</v>
+        <v>-0.785179467480787</v>
       </c>
     </row>
     <row r="1003">
@@ -12028,7 +12031,7 @@
         <v>16</v>
       </c>
       <c r="C1003" t="n">
-        <v>-0.190453061539361</v>
+        <v>-0.231495286894505</v>
       </c>
     </row>
     <row r="1004">
@@ -12039,7 +12042,7 @@
         <v>16</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.182452902669496</v>
+        <v>-0.33246614673031</v>
       </c>
     </row>
     <row r="1005">
@@ -12050,7 +12053,7 @@
         <v>16</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.324172223947676</v>
+        <v>-0.425648534887699</v>
       </c>
     </row>
     <row r="1006">
@@ -12072,7 +12075,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.70778476123911</v>
+        <v>-0.601542584628535</v>
       </c>
     </row>
     <row r="1008">
@@ -12094,7 +12097,7 @@
         <v>16</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.610472223619458</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1010">
@@ -12116,7 +12119,7 @@
         <v>16</v>
       </c>
       <c r="C1011" t="n">
-        <v>-0.110764981003546</v>
+        <v>0.157130210996434</v>
       </c>
     </row>
     <row r="1012">
@@ -12138,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.240390794680092</v>
+        <v>-0.215738097658716</v>
       </c>
     </row>
     <row r="1014">
@@ -12149,7 +12152,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.470992461582844</v>
+        <v>-18.6153553783211</v>
       </c>
     </row>
     <row r="1015">
@@ -12160,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.26996970269918</v>
+        <v>-0.196351602065292</v>
       </c>
     </row>
     <row r="1016">
@@ -12171,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.619933948277892</v>
       </c>
     </row>
     <row r="1017">
@@ -12193,7 +12196,7 @@
         <v>16</v>
       </c>
       <c r="C1018" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.265286701933789</v>
       </c>
     </row>
     <row r="1019">
@@ -12215,7 +12218,7 @@
         <v>16</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.901295450711327</v>
+        <v>-4.04057056956107</v>
       </c>
     </row>
     <row r="1021">
@@ -12226,7 +12229,7 @@
         <v>16</v>
       </c>
       <c r="C1021" t="n">
-        <v>-4.16133330024699</v>
+        <v>-1.47988942475386</v>
       </c>
     </row>
     <row r="1022">
@@ -12248,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.447017700076513</v>
+        <v>-0.528690407812271</v>
       </c>
     </row>
     <row r="1024">
@@ -12259,7 +12262,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.380079644448034</v>
+        <v>-0.260478148186584</v>
       </c>
     </row>
     <row r="1025">
@@ -12270,7 +12273,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.445855175476395</v>
+        <v>-0.410437756039064</v>
       </c>
     </row>
     <row r="1026">
@@ -12281,7 +12284,7 @@
         <v>16</v>
       </c>
       <c r="C1026" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.506799159249147</v>
       </c>
     </row>
     <row r="1027">
@@ -12292,7 +12295,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-0.171901428901499</v>
+        <v>-0.19267829739835</v>
       </c>
     </row>
     <row r="1028">
@@ -12314,7 +12317,7 @@
         <v>16</v>
       </c>
       <c r="C1029" t="n">
-        <v>-0.427125285934036</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1030">
@@ -12325,7 +12328,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.259103957944465</v>
       </c>
     </row>
     <row r="1031">
@@ -12336,7 +12339,7 @@
         <v>16</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.304388937898265</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1032">
@@ -12347,7 +12350,7 @@
         <v>16</v>
       </c>
       <c r="C1032" t="n">
-        <v>-0.252323933016838</v>
+        <v>-0.131648091648332</v>
       </c>
     </row>
     <row r="1033">
@@ -12358,7 +12361,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.39519193704484</v>
+        <v>-0.464775580549917</v>
       </c>
     </row>
     <row r="1034">
@@ -12369,7 +12372,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-4.6223506377173</v>
+        <v>-3.81860583121255</v>
       </c>
     </row>
     <row r="1035">
@@ -12380,7 +12383,7 @@
         <v>16</v>
       </c>
       <c r="C1035" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.168976535926045</v>
       </c>
     </row>
     <row r="1036">
@@ -12402,7 +12405,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>-0.204091875493667</v>
+        <v>-0.271278333003829</v>
       </c>
     </row>
     <row r="1038">
@@ -12424,7 +12427,7 @@
         <v>16</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.35266441263467</v>
+        <v>-0.711098398058194</v>
       </c>
     </row>
     <row r="1040">
@@ -12446,7 +12449,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.267326997495421</v>
       </c>
     </row>
     <row r="1042">
@@ -12457,7 +12460,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.369096354410301</v>
+        <v>-0.210239372811468</v>
       </c>
     </row>
     <row r="1043">
@@ -12468,7 +12471,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.818493991011738</v>
+        <v>-0.929933737755081</v>
       </c>
     </row>
     <row r="1044">
@@ -12479,7 +12482,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.793375731842502</v>
       </c>
     </row>
     <row r="1045">
@@ -12490,7 +12493,7 @@
         <v>16</v>
       </c>
       <c r="C1045" t="n">
-        <v>-0.202319858573526</v>
+        <v>-0.787099568133688</v>
       </c>
     </row>
     <row r="1046">
@@ -12512,7 +12515,7 @@
         <v>16</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.530027958685664</v>
       </c>
     </row>
     <row r="1048">
@@ -12534,7 +12537,7 @@
         <v>16</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.156502847977293</v>
       </c>
     </row>
     <row r="1050">
@@ -12545,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.179461918329351</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1051">
@@ -12556,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.159763313609467</v>
+        <v>-2.26276713448309</v>
       </c>
     </row>
     <row r="1052">
@@ -12578,7 +12581,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>0.105662032442489</v>
+        <v>-0.0465395693441402</v>
       </c>
     </row>
     <row r="1054">
@@ -12589,7 +12592,7 @@
         <v>16</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.151713789250719</v>
       </c>
     </row>
     <row r="1055">
@@ -12600,7 +12603,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-2.06382676524882</v>
+        <v>-6.74563320262753</v>
       </c>
     </row>
     <row r="1056">
@@ -12633,7 +12636,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.448582526429468</v>
       </c>
     </row>
     <row r="1059">
@@ -12644,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>0.0294348369977591</v>
+        <v>0.16743312327507</v>
       </c>
     </row>
     <row r="1060">
@@ -12677,7 +12680,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.384440698063473</v>
+        <v>-0.276105399959936</v>
       </c>
     </row>
     <row r="1063">
@@ -12688,7 +12691,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>0.158532264010433</v>
+        <v>-0.382227298320192</v>
       </c>
     </row>
     <row r="1064">
@@ -12710,7 +12713,7 @@
         <v>16</v>
       </c>
       <c r="C1065" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.928140472430932</v>
       </c>
     </row>
     <row r="1066">
@@ -12721,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.426877316084001</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1067">
@@ -12732,7 +12735,7 @@
         <v>16</v>
       </c>
       <c r="C1067" t="n">
-        <v>-1.64820273400489</v>
+        <v>-1.87327950292014</v>
       </c>
     </row>
     <row r="1068">
@@ -12743,7 +12746,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.265956474919591</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1069">
@@ -12754,7 +12757,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.202562240259403</v>
+        <v>-5.65349530438923</v>
       </c>
     </row>
     <row r="1070">
@@ -12765,7 +12768,7 @@
         <v>16</v>
       </c>
       <c r="C1070" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.31248608239486</v>
       </c>
     </row>
     <row r="1071">
@@ -12776,7 +12779,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.61219806249552</v>
       </c>
     </row>
     <row r="1072">
@@ -12787,7 +12790,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.78559337981808</v>
+        <v>-0.275701421888936</v>
       </c>
     </row>
     <row r="1073">
@@ -12798,7 +12801,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.185693535072687</v>
+        <v>-0.387906132241479</v>
       </c>
     </row>
     <row r="1074">
@@ -12809,7 +12812,7 @@
         <v>16</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.257984151474939</v>
+        <v>-0.356969922787726</v>
       </c>
     </row>
     <row r="1075">
@@ -12820,7 +12823,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.871372787580181</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1076">
@@ -12831,7 +12834,7 @@
         <v>16</v>
       </c>
       <c r="C1076" t="n">
-        <v>0.338544603891854</v>
+        <v>-0.0621524073199118</v>
       </c>
     </row>
     <row r="1077">
@@ -12842,7 +12845,7 @@
         <v>16</v>
       </c>
       <c r="C1077" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.84470453666744</v>
       </c>
     </row>
     <row r="1078">
@@ -12853,7 +12856,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.0815983548046233</v>
+        <v>-4.99695828253562</v>
       </c>
     </row>
     <row r="1079">
@@ -12886,7 +12889,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.159763313609468</v>
+        <v>-9.34482591404619</v>
       </c>
     </row>
     <row r="1082">
@@ -12897,7 +12900,7 @@
         <v>16</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.208390697196567</v>
+        <v>-3.20891501789518</v>
       </c>
     </row>
     <row r="1083">
@@ -12908,7 +12911,7 @@
         <v>16</v>
       </c>
       <c r="C1083" t="n">
-        <v>-1.08365442373914</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1084">
@@ -12919,7 +12922,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.278665719595887</v>
+        <v>-0.34140232195485</v>
       </c>
     </row>
     <row r="1085">
@@ -12941,7 +12944,7 @@
         <v>16</v>
       </c>
       <c r="C1086" t="n">
-        <v>0.512868000346181</v>
+        <v>-1.39659108407688</v>
       </c>
     </row>
     <row r="1087">
@@ -12952,7 +12955,7 @@
         <v>16</v>
       </c>
       <c r="C1087" t="n">
-        <v>-0.386526933630933</v>
+        <v>-0.174550022170717</v>
       </c>
     </row>
     <row r="1088">
@@ -12974,7 +12977,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>-0.0165851224388398</v>
+        <v>-0.575095598867169</v>
       </c>
     </row>
     <row r="1090">
@@ -12985,7 +12988,7 @@
         <v>16</v>
       </c>
       <c r="C1090" t="n">
-        <v>-0.167604440434132</v>
+        <v>-0.491963280234925</v>
       </c>
     </row>
     <row r="1091">
@@ -12996,7 +12999,7 @@
         <v>16</v>
       </c>
       <c r="C1091" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.01772355471365</v>
       </c>
     </row>
     <row r="1092">
@@ -13007,7 +13010,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-2.75583334889492</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1093">
@@ -13029,7 +13032,7 @@
         <v>16</v>
       </c>
       <c r="C1094" t="n">
-        <v>-0.192693909368754</v>
+        <v>-0.277459571330493</v>
       </c>
     </row>
     <row r="1095">
@@ -13040,7 +13043,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.181175626527991</v>
+        <v>-0.628415045013482</v>
       </c>
     </row>
     <row r="1096">
@@ -13062,7 +13065,7 @@
         <v>16</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.52947925701452</v>
       </c>
     </row>
     <row r="1098">
@@ -13073,7 +13076,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.494461373511641</v>
+        <v>-0.651398756095183</v>
       </c>
     </row>
     <row r="1099">
@@ -13084,7 +13087,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.197989021680995</v>
+        <v>-0.556743031551265</v>
       </c>
     </row>
     <row r="1100">
@@ -13095,7 +13098,7 @@
         <v>16</v>
       </c>
       <c r="C1100" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.68132969222546</v>
       </c>
     </row>
     <row r="1101">
@@ -13106,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-1.32521246088152</v>
+        <v>-0.72565743147351</v>
       </c>
     </row>
     <row r="1102">
@@ -13117,7 +13120,7 @@
         <v>16</v>
       </c>
       <c r="C1102" t="n">
-        <v>-0.204041532032758</v>
+        <v>-34.2164930145997</v>
       </c>
     </row>
     <row r="1103">
@@ -13128,7 +13131,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>0.235436254142511</v>
+        <v>0.176577323522272</v>
       </c>
     </row>
     <row r="1104">
@@ -13150,7 +13153,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>0.405226551183474</v>
+        <v>0.0565773823820648</v>
       </c>
     </row>
     <row r="1106">
@@ -13172,7 +13175,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.239725869013063</v>
+        <v>-1.06134678416947</v>
       </c>
     </row>
     <row r="1108">
@@ -13183,7 +13186,7 @@
         <v>16</v>
       </c>
       <c r="C1108" t="n">
-        <v>-0.278136887648125</v>
+        <v>-10.2433631489517</v>
       </c>
     </row>
     <row r="1109">
@@ -13194,7 +13197,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-4.56545513426786</v>
+        <v>-0.133600001210546</v>
       </c>
     </row>
     <row r="1110">
@@ -13216,7 +13219,7 @@
         <v>16</v>
       </c>
       <c r="C1111" t="n">
-        <v>-0.17569672916385</v>
+        <v>-0.185497508438549</v>
       </c>
     </row>
     <row r="1112">
@@ -13227,7 +13230,7 @@
         <v>16</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.159763313609468</v>
+        <v>-2.03259563420335</v>
       </c>
     </row>
     <row r="1113">
@@ -13238,7 +13241,7 @@
         <v>16</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.258424340116611</v>
+        <v>-0.187520512884013</v>
       </c>
     </row>
     <row r="1114">
@@ -13260,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.166884766572936</v>
+        <v>-0.180279915482389</v>
       </c>
     </row>
     <row r="1116">
@@ -13282,7 +13285,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-3.1716535518842</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1118">
@@ -13315,7 +13318,7 @@
         <v>16</v>
       </c>
       <c r="C1120" t="n">
-        <v>-2.44607942149383</v>
+        <v>-2.5336770957239</v>
       </c>
     </row>
     <row r="1121">
@@ -13326,7 +13329,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.641689230027555</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1122">
@@ -13337,7 +13340,7 @@
         <v>16</v>
       </c>
       <c r="C1122" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.36637503774809</v>
       </c>
     </row>
     <row r="1123">
@@ -13348,7 +13351,7 @@
         <v>16</v>
       </c>
       <c r="C1123" t="n">
-        <v>-0.179254650309116</v>
+        <v>-0.534573730069583</v>
       </c>
     </row>
     <row r="1124">
@@ -13359,7 +13362,7 @@
         <v>16</v>
       </c>
       <c r="C1124" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.587660374522523</v>
       </c>
     </row>
     <row r="1125">
@@ -13381,7 +13384,7 @@
         <v>16</v>
       </c>
       <c r="C1126" t="n">
-        <v>-0.485731786118914</v>
+        <v>-1.13252002132821</v>
       </c>
     </row>
     <row r="1127">
@@ -13392,7 +13395,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-1.61282669274869</v>
+        <v>0.583138014614039</v>
       </c>
     </row>
     <row r="1128">
@@ -13403,7 +13406,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.143863972408872</v>
       </c>
     </row>
     <row r="1129">
@@ -13414,7 +13417,7 @@
         <v>16</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.160450576621298</v>
+        <v>-0.166914701111713</v>
       </c>
     </row>
     <row r="1130">
@@ -13425,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.197884875116098</v>
+        <v>-0.17298271309923</v>
       </c>
     </row>
     <row r="1131">
@@ -13436,7 +13439,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.252580526291195</v>
+        <v>-0.226103084799333</v>
       </c>
     </row>
     <row r="1132">
@@ -13447,7 +13450,7 @@
         <v>16</v>
       </c>
       <c r="C1132" t="n">
-        <v>-0.237589811748415</v>
+        <v>-0.226684696472772</v>
       </c>
     </row>
     <row r="1133">
@@ -13458,7 +13461,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>0.610933013493727</v>
+        <v>0.252698729279369</v>
       </c>
     </row>
     <row r="1134">
@@ -13469,7 +13472,7 @@
         <v>16</v>
       </c>
       <c r="C1134" t="n">
-        <v>-0.280532458985429</v>
+        <v>-0.522255944130433</v>
       </c>
     </row>
     <row r="1135">
@@ -13480,7 +13483,7 @@
         <v>16</v>
       </c>
       <c r="C1135" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.306068995845739</v>
       </c>
     </row>
     <row r="1136">
@@ -13502,7 +13505,7 @@
         <v>16</v>
       </c>
       <c r="C1137" t="n">
-        <v>-0.275876603893388</v>
+        <v>0.287717744040911</v>
       </c>
     </row>
     <row r="1138">
@@ -13524,7 +13527,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-14.8171224189896</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1140">
@@ -13535,7 +13538,7 @@
         <v>16</v>
       </c>
       <c r="C1140" t="n">
-        <v>-0.499857644338715</v>
+        <v>-0.28196298628916</v>
       </c>
     </row>
     <row r="1141">
@@ -13546,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.195035468729866</v>
+        <v>-0.191818841787569</v>
       </c>
     </row>
     <row r="1142">
@@ -13557,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.245734507584033</v>
+        <v>-0.186097707889022</v>
       </c>
     </row>
     <row r="1143">
@@ -13579,7 +13582,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.134770012171595</v>
+        <v>-0.247877446447838</v>
       </c>
     </row>
     <row r="1145">
@@ -13590,7 +13593,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>0.186261338711304</v>
+        <v>0.24245531044842</v>
       </c>
     </row>
     <row r="1146">
@@ -13612,7 +13615,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.20322708216586</v>
       </c>
     </row>
     <row r="1148">
@@ -13623,7 +13626,7 @@
         <v>16</v>
       </c>
       <c r="C1148" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.00515779774517044</v>
       </c>
     </row>
     <row r="1149">
@@ -13634,7 +13637,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.376026280646251</v>
+        <v>-0.647729377303889</v>
       </c>
     </row>
     <row r="1150">
@@ -13645,7 +13648,7 @@
         <v>16</v>
       </c>
       <c r="C1150" t="n">
-        <v>-0.787148443438917</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1151">
@@ -13656,7 +13659,7 @@
         <v>16</v>
       </c>
       <c r="C1151" t="n">
-        <v>-0.214308069686541</v>
+        <v>-0.302805605581511</v>
       </c>
     </row>
     <row r="1152">
@@ -13667,7 +13670,7 @@
         <v>16</v>
       </c>
       <c r="C1152" t="n">
-        <v>0.00385336029833694</v>
+        <v>0.0358645604540953</v>
       </c>
     </row>
     <row r="1153">
@@ -13700,7 +13703,7 @@
         <v>16</v>
       </c>
       <c r="C1155" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.328929602895112</v>
       </c>
     </row>
     <row r="1156">
@@ -13711,7 +13714,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.860757625232887</v>
       </c>
     </row>
     <row r="1157">
@@ -13722,7 +13725,7 @@
         <v>16</v>
       </c>
       <c r="C1157" t="n">
-        <v>-0.174326536270421</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1158">
@@ -13733,7 +13736,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-1.09932904617919</v>
+        <v>0.415807220087109</v>
       </c>
     </row>
     <row r="1159">
@@ -13744,7 +13747,7 @@
         <v>16</v>
       </c>
       <c r="C1159" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.659841743030095</v>
       </c>
     </row>
     <row r="1160">
@@ -13755,7 +13758,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.314866393637221</v>
       </c>
     </row>
     <row r="1161">
@@ -13766,7 +13769,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.460559614308283</v>
+        <v>-1.73407451304088</v>
       </c>
     </row>
     <row r="1162">
@@ -13777,7 +13780,7 @@
         <v>16</v>
       </c>
       <c r="C1162" t="n">
-        <v>-0.210011925310813</v>
+        <v>-0.472843919561665</v>
       </c>
     </row>
     <row r="1163">
@@ -13788,7 +13791,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.229485505033928</v>
+        <v>-1.53654177400648</v>
       </c>
     </row>
     <row r="1164">
@@ -13810,7 +13813,7 @@
         <v>16</v>
       </c>
       <c r="C1165" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.18905930770245</v>
       </c>
     </row>
     <row r="1166">
@@ -13821,7 +13824,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.39087000527007</v>
+        <v>-1.68504875622321</v>
       </c>
     </row>
     <row r="1167">
@@ -13832,7 +13835,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.228914207685715</v>
+        <v>-0.699991555959768</v>
       </c>
     </row>
     <row r="1168">
@@ -13854,7 +13857,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.2219311515031</v>
+        <v>-0.224142292609549</v>
       </c>
     </row>
     <row r="1170">
@@ -13865,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.217665429574599</v>
+        <v>-0.946539513829572</v>
       </c>
     </row>
     <row r="1171">
@@ -13876,7 +13879,7 @@
         <v>16</v>
       </c>
       <c r="C1171" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.189040854361641</v>
       </c>
     </row>
     <row r="1172">
@@ -13887,7 +13890,7 @@
         <v>16</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.159763313609467</v>
+        <v>-3.52700741604421</v>
       </c>
     </row>
     <row r="1173">
@@ -13898,7 +13901,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.328502792541276</v>
       </c>
     </row>
     <row r="1174">
@@ -13931,7 +13934,7 @@
         <v>16</v>
       </c>
       <c r="C1176" t="n">
-        <v>-1.52076300510824</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1177">
@@ -13942,7 +13945,7 @@
         <v>16</v>
       </c>
       <c r="C1177" t="n">
-        <v>-0.189827907467134</v>
+        <v>-0.17101660835817</v>
       </c>
     </row>
     <row r="1178">
@@ -13953,7 +13956,7 @@
         <v>16</v>
       </c>
       <c r="C1178" t="n">
-        <v>-0.467909459533806</v>
+        <v>-0.0115417792007353</v>
       </c>
     </row>
     <row r="1179">
@@ -13964,7 +13967,7 @@
         <v>16</v>
       </c>
       <c r="C1179" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.82088639394377</v>
       </c>
     </row>
     <row r="1180">
@@ -13975,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.421433934014759</v>
+        <v>-0.45492487689487</v>
       </c>
     </row>
     <row r="1181">
@@ -13986,7 +13989,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.186904654654487</v>
       </c>
     </row>
     <row r="1182">
@@ -13997,7 +14000,7 @@
         <v>16</v>
       </c>
       <c r="C1182" t="n">
-        <v>-0.415239100845697</v>
+        <v>-0.131636905829593</v>
       </c>
     </row>
     <row r="1183">
@@ -14008,7 +14011,7 @@
         <v>16</v>
       </c>
       <c r="C1183" t="n">
-        <v>-0.733341541922322</v>
+        <v>-1.45727448008032</v>
       </c>
     </row>
     <row r="1184">
@@ -14019,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>0.210364545958815</v>
+        <v>-0.166814780028027</v>
       </c>
     </row>
     <row r="1185">
@@ -14030,7 +14033,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.219091552452668</v>
+        <v>-0.189032636921146</v>
       </c>
     </row>
     <row r="1186">
@@ -14041,7 +14044,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.242633667033374</v>
       </c>
     </row>
     <row r="1187">
@@ -14063,7 +14066,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.14498701386933</v>
       </c>
     </row>
     <row r="1189">
@@ -14085,7 +14088,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.465852862145819</v>
+        <v>-0.423645662803578</v>
       </c>
     </row>
     <row r="1191">
@@ -14096,7 +14099,7 @@
         <v>16</v>
       </c>
       <c r="C1191" t="n">
-        <v>-0.301131779616336</v>
+        <v>-0.326021962299551</v>
       </c>
     </row>
     <row r="1192">
@@ -14107,7 +14110,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-0.815896588689335</v>
+        <v>-1.54740669387988</v>
       </c>
     </row>
     <row r="1193">
@@ -14118,7 +14121,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.192504092130493</v>
+        <v>-0.52270542904682</v>
       </c>
     </row>
     <row r="1194">
@@ -14129,7 +14132,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.13852173173434</v>
+        <v>-0.496351759298565</v>
       </c>
     </row>
     <row r="1195">
@@ -14140,7 +14143,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>0.319507139530028</v>
+        <v>-0.465547451879337</v>
       </c>
     </row>
     <row r="1196">
@@ -14151,7 +14154,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.397299430277865</v>
+        <v>-0.327116333356472</v>
       </c>
     </row>
     <row r="1197">
@@ -14162,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.301605881784303</v>
+        <v>-0.256930768727668</v>
       </c>
     </row>
     <row r="1198">
@@ -14173,7 +14176,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>-1.76714460325053</v>
+        <v>0.142343051356217</v>
       </c>
     </row>
     <row r="1199">
@@ -14184,7 +14187,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.398975128551006</v>
+        <v>-0.690178716256802</v>
       </c>
     </row>
     <row r="1200">
@@ -14195,7 +14198,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.79723648669884</v>
+        <v>-1.15859488035184</v>
       </c>
     </row>
     <row r="1201">
@@ -14206,7 +14209,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-0.207744138419615</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
   </sheetData>
@@ -14268,7 +14271,7 @@
         <v>20.73</v>
       </c>
       <c r="E3" t="n">
-        <v>-6.80764875948651</v>
+        <v>3.73071428571428</v>
       </c>
     </row>
     <row r="4">
@@ -14523,7 +14526,7 @@
         <v>1757.71</v>
       </c>
       <c r="E18" t="n">
-        <v>-3194.45983940143</v>
+        <v>-336.555</v>
       </c>
     </row>
     <row r="19">
@@ -14948,7 +14951,7 @@
         <v>-2305.05</v>
       </c>
       <c r="E43" t="n">
-        <v>200.03</v>
+        <v>7446.70862655503</v>
       </c>
     </row>
     <row r="44">
@@ -15016,7 +15019,7 @@
         <v>1.706</v>
       </c>
       <c r="E47" t="n">
-        <v>1.83619552575525</v>
+        <v>1.9161800257675</v>
       </c>
     </row>
     <row r="48">
@@ -15033,7 +15036,7 @@
         <v>4.218</v>
       </c>
       <c r="E48" t="n">
-        <v>1.86271719290722</v>
+        <v>1.5475008513528</v>
       </c>
     </row>
     <row r="49">
@@ -15050,7 +15053,7 @@
         <v>1.578</v>
       </c>
       <c r="E49" t="n">
-        <v>1.74102883975159</v>
+        <v>1.89024183215164</v>
       </c>
     </row>
     <row r="50">
@@ -15067,7 +15070,7 @@
         <v>3.683</v>
       </c>
       <c r="E50" t="n">
-        <v>2.16718985944272</v>
+        <v>2.14099655005439</v>
       </c>
     </row>
     <row r="51">
@@ -15084,7 +15087,7 @@
         <v>2.983</v>
       </c>
       <c r="E51" t="n">
-        <v>1.70308179521709</v>
+        <v>1.54189754705531</v>
       </c>
     </row>
     <row r="52">
@@ -15101,7 +15104,7 @@
         <v>2.44</v>
       </c>
       <c r="E52" t="n">
-        <v>2.42909037877894</v>
+        <v>2.49513486254971</v>
       </c>
     </row>
     <row r="53">
@@ -15118,7 +15121,7 @@
         <v>3.879</v>
       </c>
       <c r="E53" t="n">
-        <v>2.31844328676116</v>
+        <v>2.38471802243326</v>
       </c>
     </row>
     <row r="54">
@@ -15135,7 +15138,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E54" t="n">
-        <v>1.68312337578424</v>
+        <v>1.66008139402535</v>
       </c>
     </row>
     <row r="55">
@@ -15152,7 +15155,7 @@
         <v>-1.918</v>
       </c>
       <c r="E55" t="n">
-        <v>1.47133410168301</v>
+        <v>1.49634819398512</v>
       </c>
     </row>
     <row r="56">
@@ -15169,7 +15172,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>1.86265041630776</v>
+        <v>1.7801135575068</v>
       </c>
     </row>
     <row r="57">
@@ -15186,7 +15189,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E57" t="n">
-        <v>1.45287273229855</v>
+        <v>1.54045169340159</v>
       </c>
     </row>
     <row r="58">
@@ -15203,7 +15206,7 @@
         <v>5.08900000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>5.6421079042895</v>
+        <v>3.84305580659614</v>
       </c>
     </row>
     <row r="59">
@@ -15220,7 +15223,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>1.23313271895846</v>
+        <v>2.10257142857143</v>
       </c>
     </row>
     <row r="60">
@@ -15237,7 +15240,7 @@
         <v>1.311</v>
       </c>
       <c r="E60" t="n">
-        <v>2.08629369664368</v>
+        <v>2.16719702009373</v>
       </c>
     </row>
     <row r="61">
@@ -15254,7 +15257,7 @@
         <v>2.862</v>
       </c>
       <c r="E61" t="n">
-        <v>1.84537800365152</v>
+        <v>1.82958728398572</v>
       </c>
     </row>
     <row r="62">
@@ -15373,7 +15376,7 @@
         <v>25</v>
       </c>
       <c r="E68" t="n">
-        <v>42.5</v>
+        <v>44.376393490315</v>
       </c>
     </row>
     <row r="69">
@@ -15509,7 +15512,7 @@
         <v>89</v>
       </c>
       <c r="E76" t="n">
-        <v>37.9285714285714</v>
+        <v>36.166854111281</v>
       </c>
     </row>
     <row r="77">
@@ -15611,7 +15614,7 @@
         <v>23</v>
       </c>
       <c r="E82" t="n">
-        <v>8.92307692307692</v>
+        <v>6.92737452233233</v>
       </c>
     </row>
     <row r="83">
@@ -15763,325 +15766,461 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
         <v>43</v>
       </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
       <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
         <v>44</v>
       </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
       <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
         <v>45</v>
       </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
         <v>46</v>
       </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
         <v>47</v>
       </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
       <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
         <v>48</v>
       </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
       <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
         <v>49</v>
       </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
       <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
+        <v>50</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
+        <v>52</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
+        <v>53</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="C13" t="n">
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.933333333333333</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
         <v>0.0666666666666667</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
         <v>49</v>
       </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
       <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E18" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" t="s">
         <v>52</v>
       </c>
-      <c r="D19" t="n">
+      <c r="C26" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="n">
-        <v>0.0666666666666667</v>
+      <c r="D26" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E27" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
